--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T.MOHAMMED13\Desktop\sss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A409F1-5E0A-4A78-BD45-E3313ECE5A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2B1C30-1B2E-400A-9B06-A35F19F6E4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="477">
   <si>
     <t>الأول الثانوي</t>
   </si>
@@ -1461,6 +1461,12 @@
   </si>
   <si>
     <t>taanet@hotmail.com</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>parent_phone</t>
   </si>
 </sst>
 </file>
@@ -1641,7 +1647,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1721,6 +1727,13 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ارتباط تشعبي" xfId="1" builtinId="8"/>
@@ -1743,13 +1756,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12857</xdr:col>
+      <xdr:col>12859</xdr:col>
       <xdr:colOff>270503</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12858</xdr:col>
+      <xdr:col>12860</xdr:col>
       <xdr:colOff>137153</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
@@ -1787,13 +1800,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12858</xdr:col>
+      <xdr:col>12860</xdr:col>
       <xdr:colOff>416553</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12859</xdr:col>
+      <xdr:col>12861</xdr:col>
       <xdr:colOff>283203</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
@@ -1831,13 +1844,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12862</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>16503</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12862</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>492753</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
@@ -1875,13 +1888,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12863</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>41903</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12863</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>518153</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
@@ -1919,13 +1932,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12863</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>441953</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12864</xdr:col>
+      <xdr:col>12866</xdr:col>
       <xdr:colOff>308603</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
@@ -1963,13 +1976,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12857</xdr:col>
+      <xdr:col>12859</xdr:col>
       <xdr:colOff>270503</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12858</xdr:col>
+      <xdr:col>12860</xdr:col>
       <xdr:colOff>137153</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
@@ -2007,13 +2020,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12858</xdr:col>
+      <xdr:col>12860</xdr:col>
       <xdr:colOff>416553</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12859</xdr:col>
+      <xdr:col>12861</xdr:col>
       <xdr:colOff>283203</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
@@ -2051,13 +2064,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12862</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>16503</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12862</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>492753</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
@@ -2095,13 +2108,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12863</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>41903</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12863</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>518153</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
@@ -2139,13 +2152,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12863</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>441953</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12864</xdr:col>
+      <xdr:col>12866</xdr:col>
       <xdr:colOff>308603</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
@@ -2183,13 +2196,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12858</xdr:col>
+      <xdr:col>12860</xdr:col>
       <xdr:colOff>41903</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12858</xdr:col>
+      <xdr:col>12860</xdr:col>
       <xdr:colOff>137153</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -2227,13 +2240,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12859</xdr:col>
+      <xdr:col>12861</xdr:col>
       <xdr:colOff>187953</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12859</xdr:col>
+      <xdr:col>12861</xdr:col>
       <xdr:colOff>283203</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -2271,13 +2284,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12862</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>397503</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12862</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>492753</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -2315,13 +2328,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12863</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>422903</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12863</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>518153</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -2359,13 +2372,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12864</xdr:col>
+      <xdr:col>12866</xdr:col>
       <xdr:colOff>213353</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12864</xdr:col>
+      <xdr:col>12866</xdr:col>
       <xdr:colOff>308603</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -2403,13 +2416,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12858</xdr:col>
+      <xdr:col>12860</xdr:col>
       <xdr:colOff>41903</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12858</xdr:col>
+      <xdr:col>12860</xdr:col>
       <xdr:colOff>137153</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -2447,13 +2460,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12859</xdr:col>
+      <xdr:col>12861</xdr:col>
       <xdr:colOff>187953</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12859</xdr:col>
+      <xdr:col>12861</xdr:col>
       <xdr:colOff>283203</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -2491,13 +2504,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12862</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>397503</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12862</xdr:col>
+      <xdr:col>12864</xdr:col>
       <xdr:colOff>492753</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -2535,13 +2548,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12863</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>422903</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12863</xdr:col>
+      <xdr:col>12865</xdr:col>
       <xdr:colOff>518153</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -2579,13 +2592,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12864</xdr:col>
+      <xdr:col>12866</xdr:col>
       <xdr:colOff>213353</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12864</xdr:col>
+      <xdr:col>12866</xdr:col>
       <xdr:colOff>308603</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -2937,19 +2950,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F465"/>
+  <dimension ref="A1:H465"/>
   <sheetFormatPr defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.81640625" style="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.1796875" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.08984375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.81640625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="22.6328125" style="15" customWidth="1"/>
-    <col min="6" max="6" width="22.6328125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="2"/>
+    <col min="5" max="5" width="7.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7265625" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.6328125" style="15" customWidth="1"/>
+    <col min="8" max="8" width="22.6328125" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19" customHeight="1" thickBot="1">
+    <row r="1" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2963,13 +2978,19 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.5" customHeight="1" thickBot="1">
+    <row r="2" spans="1:8" ht="19.5" customHeight="1" thickBot="1">
       <c r="A2" s="16">
         <v>1150436838</v>
       </c>
@@ -2982,14 +3003,16 @@
       <c r="D2" s="21">
         <v>1</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="24" t="s">
         <v>473</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="H2" s="25" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="19" customHeight="1" thickBot="1">
+    <row r="3" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A3" s="16">
         <v>1152217368</v>
       </c>
@@ -3002,14 +3025,16 @@
       <c r="D3" s="21">
         <v>1</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="24" t="s">
         <v>473</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="H3" s="25" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="19" customHeight="1" thickBot="1">
+    <row r="4" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A4" s="16">
         <v>1152502371</v>
       </c>
@@ -3022,14 +3047,16 @@
       <c r="D4" s="19">
         <v>1</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="24" t="s">
         <v>473</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="H4" s="25" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="19" customHeight="1" thickBot="1">
+    <row r="5" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A5" s="16">
         <v>1152327969</v>
       </c>
@@ -3042,14 +3069,16 @@
       <c r="D5" s="19">
         <v>1</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="24" t="s">
         <v>473</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="H5" s="25" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="19" customHeight="1" thickBot="1">
+    <row r="6" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A6" s="16">
         <v>2302448127</v>
       </c>
@@ -3062,14 +3091,16 @@
       <c r="D6" s="19">
         <v>1</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="24" t="s">
         <v>473</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="H6" s="25" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="19" customHeight="1" thickBot="1">
+    <row r="7" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A7" s="16">
         <v>1153472889</v>
       </c>
@@ -3082,14 +3113,16 @@
       <c r="D7" s="19">
         <v>1</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="24" t="s">
         <v>473</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="H7" s="25" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19" customHeight="1" thickBot="1">
+    <row r="8" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A8" s="16">
         <v>1152518682</v>
       </c>
@@ -3102,14 +3135,16 @@
       <c r="D8" s="19">
         <v>1</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="24" t="s">
         <v>473</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="H8" s="25" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="19" customHeight="1" thickBot="1">
+    <row r="9" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A9" s="16">
         <v>1158331023</v>
       </c>
@@ -3122,14 +3157,16 @@
       <c r="D9" s="19">
         <v>1</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="24" t="s">
         <v>473</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="H9" s="25" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="19" customHeight="1" thickBot="1">
+    <row r="10" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A10" s="16">
         <v>1157900240</v>
       </c>
@@ -3142,14 +3179,16 @@
       <c r="D10" s="19">
         <v>1</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="24" t="s">
         <v>473</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="H10" s="25" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="19" customHeight="1" thickBot="1">
+    <row r="11" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A11" s="16">
         <v>1150731048</v>
       </c>
@@ -3162,10 +3201,12 @@
       <c r="D11" s="19">
         <v>1</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A12" s="16">
         <v>2293198442</v>
       </c>
@@ -3178,10 +3219,12 @@
       <c r="D12" s="19">
         <v>1</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A13" s="16">
         <v>1174946861</v>
       </c>
@@ -3194,10 +3237,12 @@
       <c r="D13" s="19">
         <v>1</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A14" s="16">
         <v>1152820641</v>
       </c>
@@ -3210,10 +3255,12 @@
       <c r="D14" s="19">
         <v>1</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A15" s="16">
         <v>1149366963</v>
       </c>
@@ -3226,10 +3273,12 @@
       <c r="D15" s="19">
         <v>1</v>
       </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A16" s="16">
         <v>1152734123</v>
       </c>
@@ -3242,10 +3291,12 @@
       <c r="D16" s="19">
         <v>1</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A17" s="16">
         <v>1152480891</v>
       </c>
@@ -3258,10 +3309,12 @@
       <c r="D17" s="19">
         <v>1</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A18" s="16">
         <v>1153507684</v>
       </c>
@@ -3274,10 +3327,12 @@
       <c r="D18" s="19">
         <v>1</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A19" s="16">
         <v>1150008413</v>
       </c>
@@ -3290,10 +3345,12 @@
       <c r="D19" s="19">
         <v>1</v>
       </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A20" s="16">
         <v>1152989354</v>
       </c>
@@ -3306,10 +3363,12 @@
       <c r="D20" s="19">
         <v>1</v>
       </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A21" s="16">
         <v>1152061618</v>
       </c>
@@ -3322,10 +3381,12 @@
       <c r="D21" s="19">
         <v>1</v>
       </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A22" s="16">
         <v>1149206417</v>
       </c>
@@ -3338,10 +3399,12 @@
       <c r="D22" s="19">
         <v>1</v>
       </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A23" s="16">
         <v>1151880513</v>
       </c>
@@ -3354,10 +3417,12 @@
       <c r="D23" s="19">
         <v>1</v>
       </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A24" s="16">
         <v>2290421144</v>
       </c>
@@ -3370,10 +3435,12 @@
       <c r="D24" s="19">
         <v>1</v>
       </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A25" s="16">
         <v>1160061816</v>
       </c>
@@ -3386,10 +3453,12 @@
       <c r="D25" s="19">
         <v>1</v>
       </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A26" s="17">
         <v>1152890750</v>
       </c>
@@ -3402,10 +3471,12 @@
       <c r="D26" s="19">
         <v>1</v>
       </c>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A27" s="16">
         <v>1151773627</v>
       </c>
@@ -3418,10 +3489,12 @@
       <c r="D27" s="19">
         <v>1</v>
       </c>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+    </row>
+    <row r="28" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A28" s="16">
         <v>1152536601</v>
       </c>
@@ -3434,10 +3507,12 @@
       <c r="D28" s="19">
         <v>1</v>
       </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A29" s="16">
         <v>1150018610</v>
       </c>
@@ -3450,10 +3525,12 @@
       <c r="D29" s="19">
         <v>1</v>
       </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-    </row>
-    <row r="30" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A30" s="16">
         <v>1146587298</v>
       </c>
@@ -3466,10 +3543,12 @@
       <c r="D30" s="19">
         <v>1</v>
       </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-    </row>
-    <row r="31" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+    </row>
+    <row r="31" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A31" s="16">
         <v>1150743167</v>
       </c>
@@ -3482,10 +3561,12 @@
       <c r="D31" s="19">
         <v>2</v>
       </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+    </row>
+    <row r="32" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A32" s="16">
         <v>1151146907</v>
       </c>
@@ -3498,10 +3579,12 @@
       <c r="D32" s="19">
         <v>2</v>
       </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+    </row>
+    <row r="33" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A33" s="16">
         <v>2443189093</v>
       </c>
@@ -3514,10 +3597,12 @@
       <c r="D33" s="19">
         <v>2</v>
       </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+    </row>
+    <row r="34" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A34" s="16">
         <v>1151434659</v>
       </c>
@@ -3530,10 +3615,12 @@
       <c r="D34" s="19">
         <v>2</v>
       </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+    </row>
+    <row r="35" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A35" s="16">
         <v>1152565972</v>
       </c>
@@ -3546,10 +3633,12 @@
       <c r="D35" s="19">
         <v>2</v>
       </c>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+    </row>
+    <row r="36" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A36" s="16">
         <v>1154025124</v>
       </c>
@@ -3562,10 +3651,12 @@
       <c r="D36" s="19">
         <v>2</v>
       </c>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+    </row>
+    <row r="37" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A37" s="16">
         <v>1154153991</v>
       </c>
@@ -3578,10 +3669,12 @@
       <c r="D37" s="19">
         <v>2</v>
       </c>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+    </row>
+    <row r="38" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A38" s="16">
         <v>1149486605</v>
       </c>
@@ -3594,10 +3687,12 @@
       <c r="D38" s="19">
         <v>2</v>
       </c>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-    </row>
-    <row r="39" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+    </row>
+    <row r="39" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A39" s="16">
         <v>1152472815</v>
       </c>
@@ -3610,10 +3705,12 @@
       <c r="D39" s="19">
         <v>2</v>
       </c>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-    </row>
-    <row r="40" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+    </row>
+    <row r="40" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A40" s="16">
         <v>1150396164</v>
       </c>
@@ -3626,10 +3723,12 @@
       <c r="D40" s="19">
         <v>2</v>
       </c>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-    </row>
-    <row r="41" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+    </row>
+    <row r="41" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A41" s="16">
         <v>1150491064</v>
       </c>
@@ -3642,10 +3741,12 @@
       <c r="D41" s="19">
         <v>2</v>
       </c>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-    </row>
-    <row r="42" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+    </row>
+    <row r="42" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A42" s="16">
         <v>1152786958</v>
       </c>
@@ -3658,10 +3759,12 @@
       <c r="D42" s="19">
         <v>2</v>
       </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-    </row>
-    <row r="43" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+    </row>
+    <row r="43" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A43" s="16">
         <v>1149922534</v>
       </c>
@@ -3674,10 +3777,12 @@
       <c r="D43" s="19">
         <v>2</v>
       </c>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-    </row>
-    <row r="44" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+    </row>
+    <row r="44" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A44" s="16">
         <v>2269053001</v>
       </c>
@@ -3690,10 +3795,12 @@
       <c r="D44" s="19">
         <v>2</v>
       </c>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-    </row>
-    <row r="45" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+    </row>
+    <row r="45" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A45" s="16">
         <v>1157238989</v>
       </c>
@@ -3706,10 +3813,12 @@
       <c r="D45" s="19">
         <v>2</v>
       </c>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-    </row>
-    <row r="46" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E45" s="27"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+    </row>
+    <row r="46" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A46" s="16">
         <v>1153155559</v>
       </c>
@@ -3722,10 +3831,12 @@
       <c r="D46" s="19">
         <v>2</v>
       </c>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-    </row>
-    <row r="47" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+    </row>
+    <row r="47" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A47" s="16">
         <v>1149465245</v>
       </c>
@@ -3738,10 +3849,12 @@
       <c r="D47" s="19">
         <v>2</v>
       </c>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-    </row>
-    <row r="48" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+    </row>
+    <row r="48" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A48" s="16">
         <v>1155938150</v>
       </c>
@@ -3754,10 +3867,12 @@
       <c r="D48" s="19">
         <v>2</v>
       </c>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-    </row>
-    <row r="49" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+    </row>
+    <row r="49" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A49" s="16">
         <v>1149696633</v>
       </c>
@@ -3770,10 +3885,12 @@
       <c r="D49" s="19">
         <v>2</v>
       </c>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-    </row>
-    <row r="50" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+    </row>
+    <row r="50" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A50" s="16">
         <v>1155454240</v>
       </c>
@@ -3786,10 +3903,12 @@
       <c r="D50" s="19">
         <v>2</v>
       </c>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-    </row>
-    <row r="51" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+    </row>
+    <row r="51" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A51" s="16">
         <v>1150039038</v>
       </c>
@@ -3802,10 +3921,12 @@
       <c r="D51" s="19">
         <v>2</v>
       </c>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-    </row>
-    <row r="52" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E51" s="27"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+    </row>
+    <row r="52" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A52" s="16">
         <v>1152218085</v>
       </c>
@@ -3818,10 +3939,12 @@
       <c r="D52" s="19">
         <v>2</v>
       </c>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-    </row>
-    <row r="53" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E52" s="27"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+    </row>
+    <row r="53" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A53" s="16">
         <v>1147013252</v>
       </c>
@@ -3834,10 +3957,12 @@
       <c r="D53" s="19">
         <v>2</v>
       </c>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-    </row>
-    <row r="54" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+    </row>
+    <row r="54" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A54" s="16">
         <v>1154169450</v>
       </c>
@@ -3850,10 +3975,12 @@
       <c r="D54" s="19">
         <v>2</v>
       </c>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-    </row>
-    <row r="55" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E54" s="27"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+    </row>
+    <row r="55" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A55" s="16">
         <v>1151233614</v>
       </c>
@@ -3866,10 +3993,12 @@
       <c r="D55" s="19">
         <v>2</v>
       </c>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-    </row>
-    <row r="56" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+    </row>
+    <row r="56" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A56" s="16">
         <v>1151650809</v>
       </c>
@@ -3882,10 +4011,12 @@
       <c r="D56" s="19">
         <v>2</v>
       </c>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-    </row>
-    <row r="57" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+    </row>
+    <row r="57" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A57" s="16">
         <v>1151119201</v>
       </c>
@@ -3898,10 +4029,12 @@
       <c r="D57" s="19">
         <v>2</v>
       </c>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-    </row>
-    <row r="58" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+    </row>
+    <row r="58" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A58" s="16">
         <v>1152878417</v>
       </c>
@@ -3914,10 +4047,12 @@
       <c r="D58" s="19">
         <v>3</v>
       </c>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-    </row>
-    <row r="59" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+    </row>
+    <row r="59" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A59" s="16">
         <v>1152574958</v>
       </c>
@@ -3930,10 +4065,12 @@
       <c r="D59" s="19">
         <v>3</v>
       </c>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-    </row>
-    <row r="60" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+    </row>
+    <row r="60" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A60" s="16">
         <v>1152986681</v>
       </c>
@@ -3946,10 +4083,12 @@
       <c r="D60" s="19">
         <v>3</v>
       </c>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-    </row>
-    <row r="61" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+    </row>
+    <row r="61" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A61" s="16">
         <v>1151154455</v>
       </c>
@@ -3962,10 +4101,12 @@
       <c r="D61" s="19">
         <v>3</v>
       </c>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-    </row>
-    <row r="62" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+    </row>
+    <row r="62" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A62" s="16">
         <v>1159289287</v>
       </c>
@@ -3978,10 +4119,12 @@
       <c r="D62" s="19">
         <v>3</v>
       </c>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-    </row>
-    <row r="63" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E62" s="27"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+    </row>
+    <row r="63" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A63" s="16">
         <v>1153334618</v>
       </c>
@@ -3994,10 +4137,12 @@
       <c r="D63" s="19">
         <v>3</v>
       </c>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-    </row>
-    <row r="64" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E63" s="27"/>
+      <c r="F63" s="27"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+    </row>
+    <row r="64" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A64" s="16">
         <v>1152212658</v>
       </c>
@@ -4010,10 +4155,12 @@
       <c r="D64" s="19">
         <v>3</v>
       </c>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-    </row>
-    <row r="65" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E64" s="27"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+    </row>
+    <row r="65" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A65" s="16">
         <v>1152410336</v>
       </c>
@@ -4026,10 +4173,12 @@
       <c r="D65" s="19">
         <v>3</v>
       </c>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-    </row>
-    <row r="66" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+    </row>
+    <row r="66" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A66" s="16">
         <v>1154207904</v>
       </c>
@@ -4042,10 +4191,12 @@
       <c r="D66" s="19">
         <v>3</v>
       </c>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-    </row>
-    <row r="67" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E66" s="27"/>
+      <c r="F66" s="27"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+    </row>
+    <row r="67" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A67" s="16">
         <v>1168345245</v>
       </c>
@@ -4058,10 +4209,12 @@
       <c r="D67" s="19">
         <v>3</v>
       </c>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-    </row>
-    <row r="68" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E67" s="27"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+    </row>
+    <row r="68" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A68" s="16">
         <v>1149893040</v>
       </c>
@@ -4074,10 +4227,12 @@
       <c r="D68" s="19">
         <v>3</v>
       </c>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-    </row>
-    <row r="69" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E68" s="27"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+    </row>
+    <row r="69" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A69" s="16">
         <v>1151849807</v>
       </c>
@@ -4090,10 +4245,12 @@
       <c r="D69" s="19">
         <v>3</v>
       </c>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-    </row>
-    <row r="70" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E69" s="27"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+    </row>
+    <row r="70" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A70" s="16">
         <v>1152284103</v>
       </c>
@@ -4106,10 +4263,12 @@
       <c r="D70" s="19">
         <v>3</v>
       </c>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-    </row>
-    <row r="71" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E70" s="27"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+    </row>
+    <row r="71" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A71" s="16">
         <v>1167082591</v>
       </c>
@@ -4122,10 +4281,12 @@
       <c r="D71" s="19">
         <v>3</v>
       </c>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-    </row>
-    <row r="72" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E71" s="27"/>
+      <c r="F71" s="27"/>
+      <c r="G71" s="7"/>
+      <c r="H71" s="7"/>
+    </row>
+    <row r="72" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A72" s="16">
         <v>1153479645</v>
       </c>
@@ -4138,10 +4299,12 @@
       <c r="D72" s="19">
         <v>3</v>
       </c>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-    </row>
-    <row r="73" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E72" s="27"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+    </row>
+    <row r="73" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A73" s="16">
         <v>1155524893</v>
       </c>
@@ -4154,10 +4317,12 @@
       <c r="D73" s="19">
         <v>3</v>
       </c>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-    </row>
-    <row r="74" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E73" s="27"/>
+      <c r="F73" s="27"/>
+      <c r="G73" s="7"/>
+      <c r="H73" s="7"/>
+    </row>
+    <row r="74" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A74" s="16">
         <v>1150599171</v>
       </c>
@@ -4170,10 +4335,12 @@
       <c r="D74" s="19">
         <v>3</v>
       </c>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-    </row>
-    <row r="75" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E74" s="27"/>
+      <c r="F74" s="27"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+    </row>
+    <row r="75" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A75" s="16">
         <v>1154873481</v>
       </c>
@@ -4186,10 +4353,12 @@
       <c r="D75" s="19">
         <v>3</v>
       </c>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-    </row>
-    <row r="76" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E75" s="27"/>
+      <c r="F75" s="27"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+    </row>
+    <row r="76" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A76" s="16">
         <v>1152884167</v>
       </c>
@@ -4202,10 +4371,12 @@
       <c r="D76" s="19">
         <v>3</v>
       </c>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-    </row>
-    <row r="77" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E76" s="27"/>
+      <c r="F76" s="27"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+    </row>
+    <row r="77" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A77" s="16">
         <v>1152128029</v>
       </c>
@@ -4218,10 +4389,12 @@
       <c r="D77" s="19">
         <v>3</v>
       </c>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-    </row>
-    <row r="78" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E77" s="27"/>
+      <c r="F77" s="27"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+    </row>
+    <row r="78" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A78" s="16">
         <v>1151910013</v>
       </c>
@@ -4234,10 +4407,12 @@
       <c r="D78" s="19">
         <v>3</v>
       </c>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-    </row>
-    <row r="79" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E78" s="27"/>
+      <c r="F78" s="27"/>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
+    </row>
+    <row r="79" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A79" s="16">
         <v>1154287575</v>
       </c>
@@ -4250,10 +4425,12 @@
       <c r="D79" s="19">
         <v>3</v>
       </c>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-    </row>
-    <row r="80" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E79" s="27"/>
+      <c r="F79" s="27"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
+    </row>
+    <row r="80" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A80" s="16">
         <v>1152571822</v>
       </c>
@@ -4266,10 +4443,12 @@
       <c r="D80" s="19">
         <v>3</v>
       </c>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-    </row>
-    <row r="81" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E80" s="27"/>
+      <c r="F80" s="27"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+    </row>
+    <row r="81" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A81" s="16">
         <v>1150680112</v>
       </c>
@@ -4282,10 +4461,12 @@
       <c r="D81" s="19">
         <v>3</v>
       </c>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-    </row>
-    <row r="82" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E81" s="27"/>
+      <c r="F81" s="27"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+    </row>
+    <row r="82" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A82" s="16">
         <v>1150690798</v>
       </c>
@@ -4298,10 +4479,12 @@
       <c r="D82" s="19">
         <v>3</v>
       </c>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-    </row>
-    <row r="83" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E82" s="27"/>
+      <c r="F82" s="27"/>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+    </row>
+    <row r="83" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A83" s="16">
         <v>1151961511</v>
       </c>
@@ -4314,10 +4497,12 @@
       <c r="D83" s="19">
         <v>3</v>
       </c>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
-    </row>
-    <row r="84" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E83" s="27"/>
+      <c r="F83" s="27"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+    </row>
+    <row r="84" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A84" s="16">
         <v>1149761460</v>
       </c>
@@ -4330,10 +4515,12 @@
       <c r="D84" s="19">
         <v>3</v>
       </c>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
-    </row>
-    <row r="85" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E84" s="27"/>
+      <c r="F84" s="27"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+    </row>
+    <row r="85" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A85" s="16">
         <v>2297211076</v>
       </c>
@@ -4346,10 +4533,12 @@
       <c r="D85" s="19">
         <v>4</v>
       </c>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-    </row>
-    <row r="86" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E85" s="27"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="7"/>
+      <c r="H85" s="7"/>
+    </row>
+    <row r="86" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A86" s="16">
         <v>1153216211</v>
       </c>
@@ -4362,10 +4551,12 @@
       <c r="D86" s="19">
         <v>4</v>
       </c>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
-    </row>
-    <row r="87" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E86" s="27"/>
+      <c r="F86" s="27"/>
+      <c r="G86" s="7"/>
+      <c r="H86" s="7"/>
+    </row>
+    <row r="87" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A87" s="16">
         <v>1152536460</v>
       </c>
@@ -4378,10 +4569,12 @@
       <c r="D87" s="19">
         <v>4</v>
       </c>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-    </row>
-    <row r="88" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E87" s="27"/>
+      <c r="F87" s="27"/>
+      <c r="G87" s="7"/>
+      <c r="H87" s="7"/>
+    </row>
+    <row r="88" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A88" s="16">
         <v>1152152763</v>
       </c>
@@ -4394,10 +4587,12 @@
       <c r="D88" s="19">
         <v>4</v>
       </c>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
-    </row>
-    <row r="89" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E88" s="27"/>
+      <c r="F88" s="27"/>
+      <c r="G88" s="7"/>
+      <c r="H88" s="7"/>
+    </row>
+    <row r="89" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A89" s="16">
         <v>1156092080</v>
       </c>
@@ -4410,10 +4605,12 @@
       <c r="D89" s="19">
         <v>4</v>
       </c>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-    </row>
-    <row r="90" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E89" s="27"/>
+      <c r="F89" s="27"/>
+      <c r="G89" s="7"/>
+      <c r="H89" s="7"/>
+    </row>
+    <row r="90" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A90" s="16">
         <v>2510170026</v>
       </c>
@@ -4426,10 +4623,12 @@
       <c r="D90" s="19">
         <v>4</v>
       </c>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
-    </row>
-    <row r="91" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E90" s="27"/>
+      <c r="F90" s="27"/>
+      <c r="G90" s="7"/>
+      <c r="H90" s="7"/>
+    </row>
+    <row r="91" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A91" s="16">
         <v>1151404256</v>
       </c>
@@ -4442,10 +4641,12 @@
       <c r="D91" s="19">
         <v>4</v>
       </c>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-    </row>
-    <row r="92" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E91" s="27"/>
+      <c r="F91" s="27"/>
+      <c r="G91" s="7"/>
+      <c r="H91" s="7"/>
+    </row>
+    <row r="92" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A92" s="16">
         <v>1152224984</v>
       </c>
@@ -4458,10 +4659,12 @@
       <c r="D92" s="19">
         <v>4</v>
       </c>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-    </row>
-    <row r="93" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E92" s="27"/>
+      <c r="F92" s="27"/>
+      <c r="G92" s="7"/>
+      <c r="H92" s="7"/>
+    </row>
+    <row r="93" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A93" s="16">
         <v>1150781068</v>
       </c>
@@ -4474,10 +4677,12 @@
       <c r="D93" s="19">
         <v>4</v>
       </c>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-    </row>
-    <row r="94" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E93" s="27"/>
+      <c r="F93" s="27"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+    </row>
+    <row r="94" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A94" s="16">
         <v>1150218970</v>
       </c>
@@ -4490,10 +4695,12 @@
       <c r="D94" s="19">
         <v>4</v>
       </c>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
-    </row>
-    <row r="95" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E94" s="27"/>
+      <c r="F94" s="27"/>
+      <c r="G94" s="7"/>
+      <c r="H94" s="7"/>
+    </row>
+    <row r="95" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A95" s="16">
         <v>1153072044</v>
       </c>
@@ -4506,10 +4713,12 @@
       <c r="D95" s="19">
         <v>4</v>
       </c>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-    </row>
-    <row r="96" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E95" s="27"/>
+      <c r="F95" s="27"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
+    </row>
+    <row r="96" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A96" s="16">
         <v>1153072069</v>
       </c>
@@ -4522,10 +4731,12 @@
       <c r="D96" s="19">
         <v>4</v>
       </c>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
-    </row>
-    <row r="97" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E96" s="27"/>
+      <c r="F96" s="27"/>
+      <c r="G96" s="7"/>
+      <c r="H96" s="7"/>
+    </row>
+    <row r="97" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A97" s="16">
         <v>1149401059</v>
       </c>
@@ -4538,10 +4749,12 @@
       <c r="D97" s="19">
         <v>4</v>
       </c>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-    </row>
-    <row r="98" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E97" s="27"/>
+      <c r="F97" s="27"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="7"/>
+    </row>
+    <row r="98" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A98" s="16">
         <v>1153495591</v>
       </c>
@@ -4554,10 +4767,12 @@
       <c r="D98" s="19">
         <v>4</v>
       </c>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-    </row>
-    <row r="99" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E98" s="27"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="7"/>
+      <c r="H98" s="7"/>
+    </row>
+    <row r="99" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A99" s="16">
         <v>1150973210</v>
       </c>
@@ -4570,10 +4785,12 @@
       <c r="D99" s="19">
         <v>4</v>
       </c>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
-    </row>
-    <row r="100" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E99" s="27"/>
+      <c r="F99" s="27"/>
+      <c r="G99" s="7"/>
+      <c r="H99" s="7"/>
+    </row>
+    <row r="100" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A100" s="16">
         <v>1151704598</v>
       </c>
@@ -4586,10 +4803,12 @@
       <c r="D100" s="19">
         <v>4</v>
       </c>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-    </row>
-    <row r="101" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E100" s="27"/>
+      <c r="F100" s="27"/>
+      <c r="G100" s="7"/>
+      <c r="H100" s="7"/>
+    </row>
+    <row r="101" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A101" s="16">
         <v>1151845870</v>
       </c>
@@ -4602,10 +4821,12 @@
       <c r="D101" s="19">
         <v>4</v>
       </c>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-    </row>
-    <row r="102" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E101" s="27"/>
+      <c r="F101" s="27"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
+    </row>
+    <row r="102" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A102" s="16">
         <v>1149888925</v>
       </c>
@@ -4618,10 +4839,12 @@
       <c r="D102" s="19">
         <v>4</v>
       </c>
-      <c r="E102" s="7"/>
-      <c r="F102" s="7"/>
-    </row>
-    <row r="103" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E102" s="27"/>
+      <c r="F102" s="27"/>
+      <c r="G102" s="7"/>
+      <c r="H102" s="7"/>
+    </row>
+    <row r="103" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A103" s="16">
         <v>1153380116</v>
       </c>
@@ -4634,10 +4857,12 @@
       <c r="D103" s="19">
         <v>4</v>
       </c>
-      <c r="E103" s="7"/>
-      <c r="F103" s="7"/>
-    </row>
-    <row r="104" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E103" s="27"/>
+      <c r="F103" s="27"/>
+      <c r="G103" s="7"/>
+      <c r="H103" s="7"/>
+    </row>
+    <row r="104" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A104" s="16">
         <v>1152305007</v>
       </c>
@@ -4650,10 +4875,12 @@
       <c r="D104" s="19">
         <v>4</v>
       </c>
-      <c r="E104" s="7"/>
-      <c r="F104" s="7"/>
-    </row>
-    <row r="105" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E104" s="27"/>
+      <c r="F104" s="27"/>
+      <c r="G104" s="7"/>
+      <c r="H104" s="7"/>
+    </row>
+    <row r="105" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A105" s="16">
         <v>1153607922</v>
       </c>
@@ -4666,10 +4893,12 @@
       <c r="D105" s="19">
         <v>4</v>
       </c>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
-    </row>
-    <row r="106" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E105" s="27"/>
+      <c r="F105" s="27"/>
+      <c r="G105" s="7"/>
+      <c r="H105" s="7"/>
+    </row>
+    <row r="106" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A106" s="16">
         <v>1152853493</v>
       </c>
@@ -4682,10 +4911,12 @@
       <c r="D106" s="19">
         <v>4</v>
       </c>
-      <c r="E106" s="7"/>
-      <c r="F106" s="7"/>
-    </row>
-    <row r="107" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E106" s="27"/>
+      <c r="F106" s="27"/>
+      <c r="G106" s="7"/>
+      <c r="H106" s="7"/>
+    </row>
+    <row r="107" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A107" s="16">
         <v>1153534167</v>
       </c>
@@ -4698,10 +4929,12 @@
       <c r="D107" s="19">
         <v>4</v>
       </c>
-      <c r="E107" s="7"/>
-      <c r="F107" s="7"/>
-    </row>
-    <row r="108" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E107" s="27"/>
+      <c r="F107" s="27"/>
+      <c r="G107" s="7"/>
+      <c r="H107" s="7"/>
+    </row>
+    <row r="108" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A108" s="16">
         <v>1149855445</v>
       </c>
@@ -4714,10 +4947,12 @@
       <c r="D108" s="19">
         <v>4</v>
       </c>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7"/>
-    </row>
-    <row r="109" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E108" s="27"/>
+      <c r="F108" s="27"/>
+      <c r="G108" s="7"/>
+      <c r="H108" s="7"/>
+    </row>
+    <row r="109" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A109" s="16">
         <v>1153291388</v>
       </c>
@@ -4730,10 +4965,12 @@
       <c r="D109" s="19">
         <v>4</v>
       </c>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7"/>
-    </row>
-    <row r="110" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E109" s="27"/>
+      <c r="F109" s="27"/>
+      <c r="G109" s="7"/>
+      <c r="H109" s="7"/>
+    </row>
+    <row r="110" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A110" s="16">
         <v>1151814371</v>
       </c>
@@ -4746,10 +4983,12 @@
       <c r="D110" s="19">
         <v>4</v>
       </c>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7"/>
-    </row>
-    <row r="111" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E110" s="27"/>
+      <c r="F110" s="27"/>
+      <c r="G110" s="7"/>
+      <c r="H110" s="7"/>
+    </row>
+    <row r="111" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A111" s="16">
         <v>1158612646</v>
       </c>
@@ -4762,10 +5001,12 @@
       <c r="D111" s="19">
         <v>4</v>
       </c>
-      <c r="E111" s="7"/>
-      <c r="F111" s="7"/>
-    </row>
-    <row r="112" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E111" s="27"/>
+      <c r="F111" s="27"/>
+      <c r="G111" s="7"/>
+      <c r="H111" s="7"/>
+    </row>
+    <row r="112" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A112" s="16">
         <v>1151003728</v>
       </c>
@@ -4778,10 +5019,12 @@
       <c r="D112" s="19">
         <v>5</v>
       </c>
-      <c r="E112" s="7"/>
-      <c r="F112" s="7"/>
-    </row>
-    <row r="113" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E112" s="27"/>
+      <c r="F112" s="27"/>
+      <c r="G112" s="7"/>
+      <c r="H112" s="7"/>
+    </row>
+    <row r="113" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A113" s="16">
         <v>1174052116</v>
       </c>
@@ -4794,10 +5037,12 @@
       <c r="D113" s="19">
         <v>5</v>
       </c>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
-    </row>
-    <row r="114" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E113" s="27"/>
+      <c r="F113" s="27"/>
+      <c r="G113" s="7"/>
+      <c r="H113" s="7"/>
+    </row>
+    <row r="114" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A114" s="16">
         <v>1153013931</v>
       </c>
@@ -4810,10 +5055,12 @@
       <c r="D114" s="19">
         <v>5</v>
       </c>
-      <c r="E114" s="7"/>
-      <c r="F114" s="7"/>
-    </row>
-    <row r="115" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E114" s="27"/>
+      <c r="F114" s="27"/>
+      <c r="G114" s="7"/>
+      <c r="H114" s="7"/>
+    </row>
+    <row r="115" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A115" s="16">
         <v>1150396081</v>
       </c>
@@ -4826,10 +5073,12 @@
       <c r="D115" s="19">
         <v>5</v>
       </c>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
-    </row>
-    <row r="116" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E115" s="27"/>
+      <c r="F115" s="27"/>
+      <c r="G115" s="7"/>
+      <c r="H115" s="7"/>
+    </row>
+    <row r="116" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A116" s="16">
         <v>1150690699</v>
       </c>
@@ -4842,10 +5091,12 @@
       <c r="D116" s="19">
         <v>5</v>
       </c>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-    </row>
-    <row r="117" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E116" s="27"/>
+      <c r="F116" s="27"/>
+      <c r="G116" s="7"/>
+      <c r="H116" s="7"/>
+    </row>
+    <row r="117" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A117" s="16">
         <v>1152698252</v>
       </c>
@@ -4858,10 +5109,12 @@
       <c r="D117" s="19">
         <v>5</v>
       </c>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-    </row>
-    <row r="118" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E117" s="27"/>
+      <c r="F117" s="27"/>
+      <c r="G117" s="7"/>
+      <c r="H117" s="7"/>
+    </row>
+    <row r="118" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A118" s="16">
         <v>1153384795</v>
       </c>
@@ -4874,10 +5127,12 @@
       <c r="D118" s="19">
         <v>5</v>
       </c>
-      <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
-    </row>
-    <row r="119" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E118" s="27"/>
+      <c r="F118" s="27"/>
+      <c r="G118" s="7"/>
+      <c r="H118" s="7"/>
+    </row>
+    <row r="119" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A119" s="16">
         <v>1150304325</v>
       </c>
@@ -4890,10 +5145,12 @@
       <c r="D119" s="19">
         <v>5</v>
       </c>
-      <c r="E119" s="7"/>
-      <c r="F119" s="7"/>
-    </row>
-    <row r="120" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E119" s="27"/>
+      <c r="F119" s="27"/>
+      <c r="G119" s="7"/>
+      <c r="H119" s="7"/>
+    </row>
+    <row r="120" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A120" s="16">
         <v>1152915870</v>
       </c>
@@ -4906,10 +5163,12 @@
       <c r="D120" s="19">
         <v>5</v>
       </c>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
-    </row>
-    <row r="121" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E120" s="27"/>
+      <c r="F120" s="27"/>
+      <c r="G120" s="7"/>
+      <c r="H120" s="7"/>
+    </row>
+    <row r="121" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A121" s="16">
         <v>1152367700</v>
       </c>
@@ -4922,10 +5181,12 @@
       <c r="D121" s="19">
         <v>5</v>
       </c>
-      <c r="E121" s="7"/>
-      <c r="F121" s="7"/>
-    </row>
-    <row r="122" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E121" s="27"/>
+      <c r="F121" s="27"/>
+      <c r="G121" s="7"/>
+      <c r="H121" s="7"/>
+    </row>
+    <row r="122" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A122" s="16">
         <v>1152775639</v>
       </c>
@@ -4938,10 +5199,12 @@
       <c r="D122" s="19">
         <v>5</v>
       </c>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
-    </row>
-    <row r="123" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E122" s="27"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="7"/>
+      <c r="H122" s="7"/>
+    </row>
+    <row r="123" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A123" s="16">
         <v>1149182303</v>
       </c>
@@ -4954,10 +5217,12 @@
       <c r="D123" s="19">
         <v>5</v>
       </c>
-      <c r="E123" s="7"/>
-      <c r="F123" s="7"/>
-    </row>
-    <row r="124" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E123" s="27"/>
+      <c r="F123" s="27"/>
+      <c r="G123" s="7"/>
+      <c r="H123" s="7"/>
+    </row>
+    <row r="124" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A124" s="16">
         <v>1149628024</v>
       </c>
@@ -4970,10 +5235,12 @@
       <c r="D124" s="19">
         <v>5</v>
       </c>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
-    </row>
-    <row r="125" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E124" s="27"/>
+      <c r="F124" s="27"/>
+      <c r="G124" s="7"/>
+      <c r="H124" s="7"/>
+    </row>
+    <row r="125" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A125" s="16">
         <v>1152522833</v>
       </c>
@@ -4986,10 +5253,12 @@
       <c r="D125" s="19">
         <v>5</v>
       </c>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-    </row>
-    <row r="126" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E125" s="27"/>
+      <c r="F125" s="27"/>
+      <c r="G125" s="7"/>
+      <c r="H125" s="7"/>
+    </row>
+    <row r="126" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A126" s="16">
         <v>2382166136</v>
       </c>
@@ -5002,10 +5271,12 @@
       <c r="D126" s="19">
         <v>5</v>
       </c>
-      <c r="E126" s="7"/>
-      <c r="F126" s="7"/>
-    </row>
-    <row r="127" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E126" s="27"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="7"/>
+      <c r="H126" s="7"/>
+    </row>
+    <row r="127" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A127" s="16">
         <v>1151669510</v>
       </c>
@@ -5018,10 +5289,12 @@
       <c r="D127" s="19">
         <v>5</v>
       </c>
-      <c r="E127" s="7"/>
-      <c r="F127" s="7"/>
-    </row>
-    <row r="128" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E127" s="27"/>
+      <c r="F127" s="27"/>
+      <c r="G127" s="7"/>
+      <c r="H127" s="7"/>
+    </row>
+    <row r="128" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A128" s="16">
         <v>1155012543</v>
       </c>
@@ -5034,10 +5307,12 @@
       <c r="D128" s="19">
         <v>5</v>
       </c>
-      <c r="E128" s="7"/>
-      <c r="F128" s="7"/>
-    </row>
-    <row r="129" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E128" s="27"/>
+      <c r="F128" s="27"/>
+      <c r="G128" s="7"/>
+      <c r="H128" s="7"/>
+    </row>
+    <row r="129" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A129" s="16">
         <v>1150763322</v>
       </c>
@@ -5050,10 +5325,12 @@
       <c r="D129" s="19">
         <v>5</v>
       </c>
-      <c r="E129" s="7"/>
-      <c r="F129" s="7"/>
-    </row>
-    <row r="130" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E129" s="27"/>
+      <c r="F129" s="27"/>
+      <c r="G129" s="7"/>
+      <c r="H129" s="7"/>
+    </row>
+    <row r="130" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A130" s="16">
         <v>1150527107</v>
       </c>
@@ -5066,10 +5343,12 @@
       <c r="D130" s="19">
         <v>5</v>
       </c>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-    </row>
-    <row r="131" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E130" s="27"/>
+      <c r="F130" s="27"/>
+      <c r="G130" s="7"/>
+      <c r="H130" s="7"/>
+    </row>
+    <row r="131" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A131" s="16">
         <v>1171859398</v>
       </c>
@@ -5082,10 +5361,12 @@
       <c r="D131" s="19">
         <v>5</v>
       </c>
-      <c r="E131" s="7"/>
-      <c r="F131" s="7"/>
-    </row>
-    <row r="132" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E131" s="27"/>
+      <c r="F131" s="27"/>
+      <c r="G131" s="7"/>
+      <c r="H131" s="7"/>
+    </row>
+    <row r="132" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A132" s="16">
         <v>1151485529</v>
       </c>
@@ -5098,10 +5379,12 @@
       <c r="D132" s="19">
         <v>5</v>
       </c>
-      <c r="E132" s="7"/>
-      <c r="F132" s="7"/>
-    </row>
-    <row r="133" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E132" s="27"/>
+      <c r="F132" s="27"/>
+      <c r="G132" s="7"/>
+      <c r="H132" s="7"/>
+    </row>
+    <row r="133" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A133" s="16">
         <v>1153562317</v>
       </c>
@@ -5114,10 +5397,12 @@
       <c r="D133" s="19">
         <v>5</v>
       </c>
-      <c r="E133" s="7"/>
-      <c r="F133" s="7"/>
-    </row>
-    <row r="134" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E133" s="27"/>
+      <c r="F133" s="27"/>
+      <c r="G133" s="7"/>
+      <c r="H133" s="7"/>
+    </row>
+    <row r="134" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A134" s="16">
         <v>1153018385</v>
       </c>
@@ -5130,10 +5415,12 @@
       <c r="D134" s="19">
         <v>5</v>
       </c>
-      <c r="E134" s="7"/>
-      <c r="F134" s="7"/>
-    </row>
-    <row r="135" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E134" s="27"/>
+      <c r="F134" s="27"/>
+      <c r="G134" s="7"/>
+      <c r="H134" s="7"/>
+    </row>
+    <row r="135" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A135" s="16">
         <v>2288260736</v>
       </c>
@@ -5146,10 +5433,12 @@
       <c r="D135" s="19">
         <v>5</v>
       </c>
-      <c r="E135" s="7"/>
-      <c r="F135" s="7"/>
-    </row>
-    <row r="136" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E135" s="27"/>
+      <c r="F135" s="27"/>
+      <c r="G135" s="7"/>
+      <c r="H135" s="7"/>
+    </row>
+    <row r="136" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A136" s="16">
         <v>1152156905</v>
       </c>
@@ -5162,10 +5451,12 @@
       <c r="D136" s="19">
         <v>5</v>
       </c>
-      <c r="E136" s="7"/>
-      <c r="F136" s="7"/>
-    </row>
-    <row r="137" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E136" s="27"/>
+      <c r="F136" s="27"/>
+      <c r="G136" s="7"/>
+      <c r="H136" s="7"/>
+    </row>
+    <row r="137" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A137" s="16">
         <v>1152746895</v>
       </c>
@@ -5178,10 +5469,12 @@
       <c r="D137" s="19">
         <v>5</v>
       </c>
-      <c r="E137" s="7"/>
-      <c r="F137" s="7"/>
-    </row>
-    <row r="138" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E137" s="27"/>
+      <c r="F137" s="27"/>
+      <c r="G137" s="7"/>
+      <c r="H137" s="7"/>
+    </row>
+    <row r="138" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A138" s="16">
         <v>1153259260</v>
       </c>
@@ -5194,10 +5487,12 @@
       <c r="D138" s="19">
         <v>5</v>
       </c>
-      <c r="E138" s="7"/>
-      <c r="F138" s="7"/>
-    </row>
-    <row r="139" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E138" s="27"/>
+      <c r="F138" s="27"/>
+      <c r="G138" s="7"/>
+      <c r="H138" s="7"/>
+    </row>
+    <row r="139" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A139" s="16">
         <v>1153491590</v>
       </c>
@@ -5210,10 +5505,12 @@
       <c r="D139" s="19">
         <v>5</v>
       </c>
-      <c r="E139" s="7"/>
-      <c r="F139" s="7"/>
-    </row>
-    <row r="140" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E139" s="27"/>
+      <c r="F139" s="27"/>
+      <c r="G139" s="7"/>
+      <c r="H139" s="7"/>
+    </row>
+    <row r="140" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A140" s="16">
         <v>1152692925</v>
       </c>
@@ -5226,10 +5523,12 @@
       <c r="D140" s="19">
         <v>6</v>
       </c>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
-    </row>
-    <row r="141" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E140" s="27"/>
+      <c r="F140" s="27"/>
+      <c r="G140" s="7"/>
+      <c r="H140" s="7"/>
+    </row>
+    <row r="141" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A141" s="16">
         <v>1151382064</v>
       </c>
@@ -5242,10 +5541,12 @@
       <c r="D141" s="19">
         <v>6</v>
       </c>
-      <c r="E141" s="7"/>
-      <c r="F141" s="7"/>
-    </row>
-    <row r="142" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E141" s="27"/>
+      <c r="F141" s="27"/>
+      <c r="G141" s="7"/>
+      <c r="H141" s="7"/>
+    </row>
+    <row r="142" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A142" s="16">
         <v>1160032536</v>
       </c>
@@ -5258,10 +5559,12 @@
       <c r="D142" s="19">
         <v>6</v>
       </c>
-      <c r="E142" s="7"/>
-      <c r="F142" s="7"/>
-    </row>
-    <row r="143" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E142" s="27"/>
+      <c r="F142" s="27"/>
+      <c r="G142" s="7"/>
+      <c r="H142" s="7"/>
+    </row>
+    <row r="143" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A143" s="16">
         <v>1151647227</v>
       </c>
@@ -5274,10 +5577,12 @@
       <c r="D143" s="19">
         <v>6</v>
       </c>
-      <c r="E143" s="7"/>
-      <c r="F143" s="7"/>
-    </row>
-    <row r="144" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E143" s="27"/>
+      <c r="F143" s="27"/>
+      <c r="G143" s="7"/>
+      <c r="H143" s="7"/>
+    </row>
+    <row r="144" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A144" s="16">
         <v>1152706196</v>
       </c>
@@ -5290,10 +5595,12 @@
       <c r="D144" s="19">
         <v>6</v>
       </c>
-      <c r="E144" s="7"/>
-      <c r="F144" s="7"/>
-    </row>
-    <row r="145" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E144" s="27"/>
+      <c r="F144" s="27"/>
+      <c r="G144" s="7"/>
+      <c r="H144" s="7"/>
+    </row>
+    <row r="145" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A145" s="16">
         <v>1150475679</v>
       </c>
@@ -5306,10 +5613,12 @@
       <c r="D145" s="19">
         <v>6</v>
       </c>
-      <c r="E145" s="7"/>
-      <c r="F145" s="7"/>
-    </row>
-    <row r="146" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E145" s="27"/>
+      <c r="F145" s="27"/>
+      <c r="G145" s="7"/>
+      <c r="H145" s="7"/>
+    </row>
+    <row r="146" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A146" s="16">
         <v>1151259148</v>
       </c>
@@ -5322,10 +5631,12 @@
       <c r="D146" s="19">
         <v>6</v>
       </c>
-      <c r="E146" s="7"/>
-      <c r="F146" s="7"/>
-    </row>
-    <row r="147" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E146" s="27"/>
+      <c r="F146" s="27"/>
+      <c r="G146" s="7"/>
+      <c r="H146" s="7"/>
+    </row>
+    <row r="147" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A147" s="16">
         <v>1150510616</v>
       </c>
@@ -5338,10 +5649,12 @@
       <c r="D147" s="19">
         <v>6</v>
       </c>
-      <c r="E147" s="7"/>
-      <c r="F147" s="7"/>
-    </row>
-    <row r="148" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E147" s="27"/>
+      <c r="F147" s="27"/>
+      <c r="G147" s="7"/>
+      <c r="H147" s="7"/>
+    </row>
+    <row r="148" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A148" s="16">
         <v>1151026075</v>
       </c>
@@ -5354,10 +5667,12 @@
       <c r="D148" s="19">
         <v>6</v>
       </c>
-      <c r="E148" s="7"/>
-      <c r="F148" s="7"/>
-    </row>
-    <row r="149" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E148" s="27"/>
+      <c r="F148" s="27"/>
+      <c r="G148" s="7"/>
+      <c r="H148" s="7"/>
+    </row>
+    <row r="149" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A149" s="16">
         <v>1154729949</v>
       </c>
@@ -5370,10 +5685,12 @@
       <c r="D149" s="19">
         <v>6</v>
       </c>
-      <c r="E149" s="7"/>
-      <c r="F149" s="7"/>
-    </row>
-    <row r="150" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="7"/>
+      <c r="H149" s="7"/>
+    </row>
+    <row r="150" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A150" s="16">
         <v>1152363030</v>
       </c>
@@ -5386,10 +5703,12 @@
       <c r="D150" s="19">
         <v>6</v>
       </c>
-      <c r="E150" s="7"/>
-      <c r="F150" s="7"/>
-    </row>
-    <row r="151" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E150" s="27"/>
+      <c r="F150" s="27"/>
+      <c r="G150" s="7"/>
+      <c r="H150" s="7"/>
+    </row>
+    <row r="151" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A151" s="16">
         <v>1152884464</v>
       </c>
@@ -5402,10 +5721,12 @@
       <c r="D151" s="19">
         <v>6</v>
       </c>
-      <c r="E151" s="7"/>
-      <c r="F151" s="7"/>
-    </row>
-    <row r="152" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E151" s="27"/>
+      <c r="F151" s="27"/>
+      <c r="G151" s="7"/>
+      <c r="H151" s="7"/>
+    </row>
+    <row r="152" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A152" s="16">
         <v>1150508719</v>
       </c>
@@ -5418,10 +5739,12 @@
       <c r="D152" s="19">
         <v>6</v>
       </c>
-      <c r="E152" s="7"/>
-      <c r="F152" s="7"/>
-    </row>
-    <row r="153" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E152" s="27"/>
+      <c r="F152" s="27"/>
+      <c r="G152" s="7"/>
+      <c r="H152" s="7"/>
+    </row>
+    <row r="153" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A153" s="16">
         <v>1148670639</v>
       </c>
@@ -5434,10 +5757,12 @@
       <c r="D153" s="19">
         <v>6</v>
       </c>
-      <c r="E153" s="7"/>
-      <c r="F153" s="7"/>
-    </row>
-    <row r="154" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E153" s="27"/>
+      <c r="F153" s="27"/>
+      <c r="G153" s="7"/>
+      <c r="H153" s="7"/>
+    </row>
+    <row r="154" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A154" s="16">
         <v>1150839437</v>
       </c>
@@ -5450,10 +5775,12 @@
       <c r="D154" s="19">
         <v>6</v>
       </c>
-      <c r="E154" s="7"/>
-      <c r="F154" s="7"/>
-    </row>
-    <row r="155" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E154" s="27"/>
+      <c r="F154" s="27"/>
+      <c r="G154" s="7"/>
+      <c r="H154" s="7"/>
+    </row>
+    <row r="155" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A155" s="16">
         <v>1153716194</v>
       </c>
@@ -5466,10 +5793,12 @@
       <c r="D155" s="19">
         <v>6</v>
       </c>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7"/>
-    </row>
-    <row r="156" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E155" s="27"/>
+      <c r="F155" s="27"/>
+      <c r="G155" s="7"/>
+      <c r="H155" s="7"/>
+    </row>
+    <row r="156" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A156" s="16">
         <v>1150274379</v>
       </c>
@@ -5482,10 +5811,12 @@
       <c r="D156" s="19">
         <v>6</v>
       </c>
-      <c r="E156" s="7"/>
-      <c r="F156" s="7"/>
-    </row>
-    <row r="157" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E156" s="27"/>
+      <c r="F156" s="27"/>
+      <c r="G156" s="7"/>
+      <c r="H156" s="7"/>
+    </row>
+    <row r="157" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A157" s="16">
         <v>1153130289</v>
       </c>
@@ -5498,10 +5829,12 @@
       <c r="D157" s="19">
         <v>6</v>
       </c>
-      <c r="E157" s="7"/>
-      <c r="F157" s="7"/>
-    </row>
-    <row r="158" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E157" s="27"/>
+      <c r="F157" s="27"/>
+      <c r="G157" s="7"/>
+      <c r="H157" s="7"/>
+    </row>
+    <row r="158" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A158" s="16">
         <v>1150249041</v>
       </c>
@@ -5514,10 +5847,12 @@
       <c r="D158" s="19">
         <v>6</v>
       </c>
-      <c r="E158" s="7"/>
-      <c r="F158" s="7"/>
-    </row>
-    <row r="159" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E158" s="27"/>
+      <c r="F158" s="27"/>
+      <c r="G158" s="7"/>
+      <c r="H158" s="7"/>
+    </row>
+    <row r="159" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A159" s="16">
         <v>1150925269</v>
       </c>
@@ -5530,10 +5865,12 @@
       <c r="D159" s="19">
         <v>6</v>
       </c>
-      <c r="E159" s="7"/>
-      <c r="F159" s="7"/>
-    </row>
-    <row r="160" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E159" s="27"/>
+      <c r="F159" s="27"/>
+      <c r="G159" s="7"/>
+      <c r="H159" s="7"/>
+    </row>
+    <row r="160" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A160" s="16">
         <v>1150972576</v>
       </c>
@@ -5546,10 +5883,12 @@
       <c r="D160" s="19">
         <v>6</v>
       </c>
-      <c r="E160" s="7"/>
-      <c r="F160" s="7"/>
-    </row>
-    <row r="161" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E160" s="27"/>
+      <c r="F160" s="27"/>
+      <c r="G160" s="7"/>
+      <c r="H160" s="7"/>
+    </row>
+    <row r="161" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A161" s="16">
         <v>1150576450</v>
       </c>
@@ -5562,10 +5901,12 @@
       <c r="D161" s="19">
         <v>6</v>
       </c>
-      <c r="E161" s="7"/>
-      <c r="F161" s="7"/>
-    </row>
-    <row r="162" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E161" s="27"/>
+      <c r="F161" s="27"/>
+      <c r="G161" s="7"/>
+      <c r="H161" s="7"/>
+    </row>
+    <row r="162" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A162" s="16">
         <v>1152225353</v>
       </c>
@@ -5578,10 +5919,12 @@
       <c r="D162" s="19">
         <v>6</v>
       </c>
-      <c r="E162" s="7"/>
-      <c r="F162" s="7"/>
-    </row>
-    <row r="163" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E162" s="27"/>
+      <c r="F162" s="27"/>
+      <c r="G162" s="7"/>
+      <c r="H162" s="7"/>
+    </row>
+    <row r="163" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A163" s="16">
         <v>1149840363</v>
       </c>
@@ -5594,10 +5937,12 @@
       <c r="D163" s="19">
         <v>6</v>
       </c>
-      <c r="E163" s="7"/>
-      <c r="F163" s="7"/>
-    </row>
-    <row r="164" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E163" s="27"/>
+      <c r="F163" s="27"/>
+      <c r="G163" s="7"/>
+      <c r="H163" s="7"/>
+    </row>
+    <row r="164" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A164" s="16">
         <v>1153189889</v>
       </c>
@@ -5610,10 +5955,12 @@
       <c r="D164" s="19">
         <v>6</v>
       </c>
-      <c r="E164" s="7"/>
-      <c r="F164" s="7"/>
-    </row>
-    <row r="165" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E164" s="27"/>
+      <c r="F164" s="27"/>
+      <c r="G164" s="7"/>
+      <c r="H164" s="7"/>
+    </row>
+    <row r="165" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A165" s="16">
         <v>1153243926</v>
       </c>
@@ -5626,10 +5973,12 @@
       <c r="D165" s="19">
         <v>6</v>
       </c>
-      <c r="E165" s="7"/>
-      <c r="F165" s="7"/>
-    </row>
-    <row r="166" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E165" s="27"/>
+      <c r="F165" s="27"/>
+      <c r="G165" s="7"/>
+      <c r="H165" s="7"/>
+    </row>
+    <row r="166" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A166" s="16">
         <v>1149713255</v>
       </c>
@@ -5642,10 +5991,12 @@
       <c r="D166" s="19">
         <v>6</v>
       </c>
-      <c r="E166" s="7"/>
-      <c r="F166" s="7"/>
-    </row>
-    <row r="167" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E166" s="27"/>
+      <c r="F166" s="27"/>
+      <c r="G166" s="7"/>
+      <c r="H166" s="7"/>
+    </row>
+    <row r="167" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A167" s="16">
         <v>1149713412</v>
       </c>
@@ -5658,10 +6009,12 @@
       <c r="D167" s="19">
         <v>6</v>
       </c>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7"/>
-    </row>
-    <row r="168" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E167" s="27"/>
+      <c r="F167" s="27"/>
+      <c r="G167" s="7"/>
+      <c r="H167" s="7"/>
+    </row>
+    <row r="168" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A168" s="16">
         <v>1148755273</v>
       </c>
@@ -5674,10 +6027,12 @@
       <c r="D168" s="19">
         <v>1</v>
       </c>
-      <c r="E168" s="7"/>
-      <c r="F168" s="7"/>
-    </row>
-    <row r="169" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E168" s="27"/>
+      <c r="F168" s="27"/>
+      <c r="G168" s="7"/>
+      <c r="H168" s="7"/>
+    </row>
+    <row r="169" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A169" s="16">
         <v>1146774821</v>
       </c>
@@ -5690,10 +6045,12 @@
       <c r="D169" s="19">
         <v>1</v>
       </c>
-      <c r="E169" s="7"/>
-      <c r="F169" s="7"/>
-    </row>
-    <row r="170" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E169" s="27"/>
+      <c r="F169" s="27"/>
+      <c r="G169" s="7"/>
+      <c r="H169" s="7"/>
+    </row>
+    <row r="170" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A170" s="16">
         <v>1146165780</v>
       </c>
@@ -5706,10 +6063,12 @@
       <c r="D170" s="19">
         <v>1</v>
       </c>
-      <c r="E170" s="7"/>
-      <c r="F170" s="7"/>
-    </row>
-    <row r="171" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E170" s="27"/>
+      <c r="F170" s="27"/>
+      <c r="G170" s="7"/>
+      <c r="H170" s="7"/>
+    </row>
+    <row r="171" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A171" s="16">
         <v>1147913071</v>
       </c>
@@ -5722,10 +6081,12 @@
       <c r="D171" s="19">
         <v>1</v>
       </c>
-      <c r="E171" s="7"/>
-      <c r="F171" s="7"/>
-    </row>
-    <row r="172" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E171" s="27"/>
+      <c r="F171" s="27"/>
+      <c r="G171" s="7"/>
+      <c r="H171" s="7"/>
+    </row>
+    <row r="172" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A172" s="16">
         <v>1149665844</v>
       </c>
@@ -5738,10 +6099,12 @@
       <c r="D172" s="19">
         <v>1</v>
       </c>
-      <c r="E172" s="7"/>
-      <c r="F172" s="7"/>
-    </row>
-    <row r="173" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E172" s="27"/>
+      <c r="F172" s="27"/>
+      <c r="G172" s="7"/>
+      <c r="H172" s="7"/>
+    </row>
+    <row r="173" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A173" s="16">
         <v>2282375720</v>
       </c>
@@ -5754,10 +6117,12 @@
       <c r="D173" s="19">
         <v>1</v>
       </c>
-      <c r="E173" s="7"/>
-      <c r="F173" s="7"/>
-    </row>
-    <row r="174" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E173" s="27"/>
+      <c r="F173" s="27"/>
+      <c r="G173" s="7"/>
+      <c r="H173" s="7"/>
+    </row>
+    <row r="174" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A174" s="16">
         <v>2415139746</v>
       </c>
@@ -5770,10 +6135,12 @@
       <c r="D174" s="19">
         <v>1</v>
       </c>
-      <c r="E174" s="7"/>
-      <c r="F174" s="7"/>
-    </row>
-    <row r="175" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E174" s="27"/>
+      <c r="F174" s="27"/>
+      <c r="G174" s="7"/>
+      <c r="H174" s="7"/>
+    </row>
+    <row r="175" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A175" s="16">
         <v>1146628035</v>
       </c>
@@ -5786,10 +6153,12 @@
       <c r="D175" s="19">
         <v>1</v>
       </c>
-      <c r="E175" s="7"/>
-      <c r="F175" s="7"/>
-    </row>
-    <row r="176" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E175" s="27"/>
+      <c r="F175" s="27"/>
+      <c r="G175" s="7"/>
+      <c r="H175" s="7"/>
+    </row>
+    <row r="176" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A176" s="16">
         <v>1148873159</v>
       </c>
@@ -5802,10 +6171,12 @@
       <c r="D176" s="19">
         <v>1</v>
       </c>
-      <c r="E176" s="7"/>
-      <c r="F176" s="7"/>
-    </row>
-    <row r="177" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E176" s="27"/>
+      <c r="F176" s="27"/>
+      <c r="G176" s="7"/>
+      <c r="H176" s="7"/>
+    </row>
+    <row r="177" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A177" s="16">
         <v>2275349674</v>
       </c>
@@ -5818,10 +6189,12 @@
       <c r="D177" s="19">
         <v>1</v>
       </c>
-      <c r="E177" s="7"/>
-      <c r="F177" s="7"/>
-    </row>
-    <row r="178" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E177" s="27"/>
+      <c r="F177" s="27"/>
+      <c r="G177" s="7"/>
+      <c r="H177" s="7"/>
+    </row>
+    <row r="178" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A178" s="16">
         <v>1145487730</v>
       </c>
@@ -5834,10 +6207,12 @@
       <c r="D178" s="19">
         <v>1</v>
       </c>
-      <c r="E178" s="7"/>
-      <c r="F178" s="7"/>
-    </row>
-    <row r="179" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E178" s="27"/>
+      <c r="F178" s="27"/>
+      <c r="G178" s="7"/>
+      <c r="H178" s="7"/>
+    </row>
+    <row r="179" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A179" s="16">
         <v>1146809536</v>
       </c>
@@ -5850,10 +6225,12 @@
       <c r="D179" s="19">
         <v>1</v>
       </c>
-      <c r="E179" s="7"/>
-      <c r="F179" s="7"/>
-    </row>
-    <row r="180" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E179" s="27"/>
+      <c r="F179" s="27"/>
+      <c r="G179" s="7"/>
+      <c r="H179" s="7"/>
+    </row>
+    <row r="180" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A180" s="16">
         <v>1164976993</v>
       </c>
@@ -5866,10 +6243,12 @@
       <c r="D180" s="19">
         <v>1</v>
       </c>
-      <c r="E180" s="7"/>
-      <c r="F180" s="7"/>
-    </row>
-    <row r="181" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E180" s="27"/>
+      <c r="F180" s="27"/>
+      <c r="G180" s="7"/>
+      <c r="H180" s="7"/>
+    </row>
+    <row r="181" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A181" s="16">
         <v>1146821820</v>
       </c>
@@ -5882,10 +6261,12 @@
       <c r="D181" s="19">
         <v>1</v>
       </c>
-      <c r="E181" s="7"/>
-      <c r="F181" s="7"/>
-    </row>
-    <row r="182" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E181" s="27"/>
+      <c r="F181" s="27"/>
+      <c r="G181" s="7"/>
+      <c r="H181" s="7"/>
+    </row>
+    <row r="182" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A182" s="16">
         <v>1146526668</v>
       </c>
@@ -5898,10 +6279,12 @@
       <c r="D182" s="19">
         <v>1</v>
       </c>
-      <c r="E182" s="7"/>
-      <c r="F182" s="7"/>
-    </row>
-    <row r="183" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E182" s="27"/>
+      <c r="F182" s="27"/>
+      <c r="G182" s="7"/>
+      <c r="H182" s="7"/>
+    </row>
+    <row r="183" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A183" s="16">
         <v>1149762419</v>
       </c>
@@ -5914,10 +6297,12 @@
       <c r="D183" s="19">
         <v>1</v>
       </c>
-      <c r="E183" s="7"/>
-      <c r="F183" s="7"/>
-    </row>
-    <row r="184" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E183" s="27"/>
+      <c r="F183" s="27"/>
+      <c r="G183" s="7"/>
+      <c r="H183" s="7"/>
+    </row>
+    <row r="184" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A184" s="16">
         <v>1146972862</v>
       </c>
@@ -5930,10 +6315,12 @@
       <c r="D184" s="19">
         <v>1</v>
       </c>
-      <c r="E184" s="7"/>
-      <c r="F184" s="7"/>
-    </row>
-    <row r="185" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E184" s="27"/>
+      <c r="F184" s="27"/>
+      <c r="G184" s="7"/>
+      <c r="H184" s="7"/>
+    </row>
+    <row r="185" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A185" s="16">
         <v>1148273418</v>
       </c>
@@ -5946,10 +6333,12 @@
       <c r="D185" s="19">
         <v>1</v>
       </c>
-      <c r="E185" s="7"/>
-      <c r="F185" s="7"/>
-    </row>
-    <row r="186" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E185" s="27"/>
+      <c r="F185" s="27"/>
+      <c r="G185" s="7"/>
+      <c r="H185" s="7"/>
+    </row>
+    <row r="186" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A186" s="16">
         <v>1148688326</v>
       </c>
@@ -5962,10 +6351,12 @@
       <c r="D186" s="19">
         <v>1</v>
       </c>
-      <c r="E186" s="7"/>
-      <c r="F186" s="7"/>
-    </row>
-    <row r="187" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E186" s="27"/>
+      <c r="F186" s="27"/>
+      <c r="G186" s="7"/>
+      <c r="H186" s="7"/>
+    </row>
+    <row r="187" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A187" s="16">
         <v>1146775844</v>
       </c>
@@ -5978,10 +6369,12 @@
       <c r="D187" s="19">
         <v>1</v>
       </c>
-      <c r="E187" s="7"/>
-      <c r="F187" s="7"/>
-    </row>
-    <row r="188" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E187" s="27"/>
+      <c r="F187" s="27"/>
+      <c r="G187" s="7"/>
+      <c r="H187" s="7"/>
+    </row>
+    <row r="188" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A188" s="16">
         <v>2344822255</v>
       </c>
@@ -5994,10 +6387,12 @@
       <c r="D188" s="19">
         <v>1</v>
       </c>
-      <c r="E188" s="7"/>
-      <c r="F188" s="7"/>
-    </row>
-    <row r="189" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E188" s="27"/>
+      <c r="F188" s="27"/>
+      <c r="G188" s="7"/>
+      <c r="H188" s="7"/>
+    </row>
+    <row r="189" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A189" s="16">
         <v>1150838223</v>
       </c>
@@ -6010,10 +6405,12 @@
       <c r="D189" s="19">
         <v>1</v>
       </c>
-      <c r="E189" s="7"/>
-      <c r="F189" s="7"/>
-    </row>
-    <row r="190" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E189" s="27"/>
+      <c r="F189" s="27"/>
+      <c r="G189" s="7"/>
+      <c r="H189" s="7"/>
+    </row>
+    <row r="190" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A190" s="16">
         <v>1146376064</v>
       </c>
@@ -6026,10 +6423,12 @@
       <c r="D190" s="19">
         <v>1</v>
       </c>
-      <c r="E190" s="7"/>
-      <c r="F190" s="7"/>
-    </row>
-    <row r="191" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E190" s="27"/>
+      <c r="F190" s="27"/>
+      <c r="G190" s="7"/>
+      <c r="H190" s="7"/>
+    </row>
+    <row r="191" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A191" s="16">
         <v>1144789813</v>
       </c>
@@ -6042,10 +6441,12 @@
       <c r="D191" s="19">
         <v>1</v>
       </c>
-      <c r="E191" s="7"/>
-      <c r="F191" s="7"/>
-    </row>
-    <row r="192" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E191" s="27"/>
+      <c r="F191" s="27"/>
+      <c r="G191" s="7"/>
+      <c r="H191" s="7"/>
+    </row>
+    <row r="192" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A192" s="16">
         <v>1146471519</v>
       </c>
@@ -6058,10 +6459,12 @@
       <c r="D192" s="19">
         <v>1</v>
       </c>
-      <c r="E192" s="7"/>
-      <c r="F192" s="7"/>
-    </row>
-    <row r="193" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E192" s="27"/>
+      <c r="F192" s="27"/>
+      <c r="G192" s="7"/>
+      <c r="H192" s="7"/>
+    </row>
+    <row r="193" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A193" s="16">
         <v>1145431654</v>
       </c>
@@ -6074,10 +6477,12 @@
       <c r="D193" s="19">
         <v>1</v>
       </c>
-      <c r="E193" s="7"/>
-      <c r="F193" s="7"/>
-    </row>
-    <row r="194" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E193" s="27"/>
+      <c r="F193" s="27"/>
+      <c r="G193" s="7"/>
+      <c r="H193" s="7"/>
+    </row>
+    <row r="194" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A194" s="16">
         <v>1148252990</v>
       </c>
@@ -6090,10 +6495,12 @@
       <c r="D194" s="19">
         <v>2</v>
       </c>
-      <c r="E194" s="7"/>
-      <c r="F194" s="7"/>
-    </row>
-    <row r="195" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E194" s="27"/>
+      <c r="F194" s="27"/>
+      <c r="G194" s="7"/>
+      <c r="H194" s="7"/>
+    </row>
+    <row r="195" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A195" s="16">
         <v>1149306225</v>
       </c>
@@ -6106,10 +6513,12 @@
       <c r="D195" s="19">
         <v>2</v>
       </c>
-      <c r="E195" s="7"/>
-      <c r="F195" s="7"/>
-    </row>
-    <row r="196" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E195" s="27"/>
+      <c r="F195" s="27"/>
+      <c r="G195" s="7"/>
+      <c r="H195" s="7"/>
+    </row>
+    <row r="196" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A196" s="16">
         <v>1151264437</v>
       </c>
@@ -6122,10 +6531,12 @@
       <c r="D196" s="19">
         <v>2</v>
       </c>
-      <c r="E196" s="7"/>
-      <c r="F196" s="7"/>
-    </row>
-    <row r="197" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E196" s="27"/>
+      <c r="F196" s="27"/>
+      <c r="G196" s="7"/>
+      <c r="H196" s="7"/>
+    </row>
+    <row r="197" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A197" s="16">
         <v>1150158754</v>
       </c>
@@ -6138,10 +6549,12 @@
       <c r="D197" s="19">
         <v>2</v>
       </c>
-      <c r="E197" s="7"/>
-      <c r="F197" s="7"/>
-    </row>
-    <row r="198" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E197" s="27"/>
+      <c r="F197" s="27"/>
+      <c r="G197" s="7"/>
+      <c r="H197" s="7"/>
+    </row>
+    <row r="198" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A198" s="16">
         <v>1148596271</v>
       </c>
@@ -6154,10 +6567,12 @@
       <c r="D198" s="19">
         <v>2</v>
       </c>
-      <c r="E198" s="7"/>
-      <c r="F198" s="7"/>
-    </row>
-    <row r="199" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E198" s="27"/>
+      <c r="F198" s="27"/>
+      <c r="G198" s="7"/>
+      <c r="H198" s="7"/>
+    </row>
+    <row r="199" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A199" s="16">
         <v>1147407355</v>
       </c>
@@ -6170,10 +6585,12 @@
       <c r="D199" s="19">
         <v>2</v>
       </c>
-      <c r="E199" s="7"/>
-      <c r="F199" s="7"/>
-    </row>
-    <row r="200" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E199" s="27"/>
+      <c r="F199" s="27"/>
+      <c r="G199" s="7"/>
+      <c r="H199" s="7"/>
+    </row>
+    <row r="200" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A200" s="16">
         <v>1146987373</v>
       </c>
@@ -6186,10 +6603,12 @@
       <c r="D200" s="19">
         <v>2</v>
       </c>
-      <c r="E200" s="7"/>
-      <c r="F200" s="7"/>
-    </row>
-    <row r="201" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E200" s="27"/>
+      <c r="F200" s="27"/>
+      <c r="G200" s="7"/>
+      <c r="H200" s="7"/>
+    </row>
+    <row r="201" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A201" s="16">
         <v>1142858388</v>
       </c>
@@ -6202,10 +6621,12 @@
       <c r="D201" s="19">
         <v>2</v>
       </c>
-      <c r="E201" s="7"/>
-      <c r="F201" s="7"/>
-    </row>
-    <row r="202" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E201" s="27"/>
+      <c r="F201" s="27"/>
+      <c r="G201" s="7"/>
+      <c r="H201" s="7"/>
+    </row>
+    <row r="202" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A202" s="16">
         <v>1148535568</v>
       </c>
@@ -6218,10 +6639,12 @@
       <c r="D202" s="19">
         <v>2</v>
       </c>
-      <c r="E202" s="7"/>
-      <c r="F202" s="7"/>
-    </row>
-    <row r="203" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E202" s="27"/>
+      <c r="F202" s="27"/>
+      <c r="G202" s="7"/>
+      <c r="H202" s="7"/>
+    </row>
+    <row r="203" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A203" s="16">
         <v>1147255028</v>
       </c>
@@ -6234,10 +6657,12 @@
       <c r="D203" s="19">
         <v>2</v>
       </c>
-      <c r="E203" s="7"/>
-      <c r="F203" s="7"/>
-    </row>
-    <row r="204" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E203" s="27"/>
+      <c r="F203" s="27"/>
+      <c r="G203" s="7"/>
+      <c r="H203" s="7"/>
+    </row>
+    <row r="204" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A204" s="16">
         <v>1147682353</v>
       </c>
@@ -6250,10 +6675,12 @@
       <c r="D204" s="19">
         <v>2</v>
       </c>
-      <c r="E204" s="7"/>
-      <c r="F204" s="7"/>
-    </row>
-    <row r="205" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E204" s="27"/>
+      <c r="F204" s="27"/>
+      <c r="G204" s="7"/>
+      <c r="H204" s="7"/>
+    </row>
+    <row r="205" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A205" s="16">
         <v>1146380868</v>
       </c>
@@ -6266,10 +6693,12 @@
       <c r="D205" s="19">
         <v>2</v>
       </c>
-      <c r="E205" s="7"/>
-      <c r="F205" s="7"/>
-    </row>
-    <row r="206" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E205" s="27"/>
+      <c r="F205" s="27"/>
+      <c r="G205" s="7"/>
+      <c r="H205" s="7"/>
+    </row>
+    <row r="206" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A206" s="16">
         <v>1149234906</v>
       </c>
@@ -6282,10 +6711,12 @@
       <c r="D206" s="19">
         <v>2</v>
       </c>
-      <c r="E206" s="7"/>
-      <c r="F206" s="7"/>
-    </row>
-    <row r="207" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E206" s="27"/>
+      <c r="F206" s="27"/>
+      <c r="G206" s="7"/>
+      <c r="H206" s="7"/>
+    </row>
+    <row r="207" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A207" s="16">
         <v>1145460539</v>
       </c>
@@ -6298,10 +6729,12 @@
       <c r="D207" s="19">
         <v>2</v>
       </c>
-      <c r="E207" s="7"/>
-      <c r="F207" s="7"/>
-    </row>
-    <row r="208" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E207" s="27"/>
+      <c r="F207" s="27"/>
+      <c r="G207" s="7"/>
+      <c r="H207" s="7"/>
+    </row>
+    <row r="208" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A208" s="16">
         <v>1146879539</v>
       </c>
@@ -6314,10 +6747,12 @@
       <c r="D208" s="19">
         <v>2</v>
       </c>
-      <c r="E208" s="7"/>
-      <c r="F208" s="7"/>
-    </row>
-    <row r="209" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E208" s="27"/>
+      <c r="F208" s="27"/>
+      <c r="G208" s="7"/>
+      <c r="H208" s="7"/>
+    </row>
+    <row r="209" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A209" s="16">
         <v>1146061013</v>
       </c>
@@ -6330,10 +6765,12 @@
       <c r="D209" s="19">
         <v>2</v>
       </c>
-      <c r="E209" s="7"/>
-      <c r="F209" s="7"/>
-    </row>
-    <row r="210" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E209" s="27"/>
+      <c r="F209" s="27"/>
+      <c r="G209" s="7"/>
+      <c r="H209" s="7"/>
+    </row>
+    <row r="210" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A210" s="16">
         <v>1161327497</v>
       </c>
@@ -6346,10 +6783,12 @@
       <c r="D210" s="19">
         <v>2</v>
       </c>
-      <c r="E210" s="7"/>
-      <c r="F210" s="7"/>
-    </row>
-    <row r="211" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E210" s="27"/>
+      <c r="F210" s="27"/>
+      <c r="G210" s="7"/>
+      <c r="H210" s="7"/>
+    </row>
+    <row r="211" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A211" s="16">
         <v>1146546294</v>
       </c>
@@ -6362,10 +6801,12 @@
       <c r="D211" s="19">
         <v>2</v>
       </c>
-      <c r="E211" s="7"/>
-      <c r="F211" s="7"/>
-    </row>
-    <row r="212" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E211" s="27"/>
+      <c r="F211" s="27"/>
+      <c r="G211" s="7"/>
+      <c r="H211" s="7"/>
+    </row>
+    <row r="212" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A212" s="16">
         <v>1147314809</v>
       </c>
@@ -6378,10 +6819,12 @@
       <c r="D212" s="19">
         <v>2</v>
       </c>
-      <c r="E212" s="7"/>
-      <c r="F212" s="7"/>
-    </row>
-    <row r="213" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E212" s="27"/>
+      <c r="F212" s="27"/>
+      <c r="G212" s="7"/>
+      <c r="H212" s="7"/>
+    </row>
+    <row r="213" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A213" s="16">
         <v>1148907890</v>
       </c>
@@ -6394,10 +6837,12 @@
       <c r="D213" s="19">
         <v>2</v>
       </c>
-      <c r="E213" s="7"/>
-      <c r="F213" s="7"/>
-    </row>
-    <row r="214" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E213" s="27"/>
+      <c r="F213" s="27"/>
+      <c r="G213" s="7"/>
+      <c r="H213" s="7"/>
+    </row>
+    <row r="214" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A214" s="16">
         <v>1148220138</v>
       </c>
@@ -6410,10 +6855,12 @@
       <c r="D214" s="19">
         <v>2</v>
       </c>
-      <c r="E214" s="7"/>
-      <c r="F214" s="7"/>
-    </row>
-    <row r="215" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E214" s="27"/>
+      <c r="F214" s="27"/>
+      <c r="G214" s="7"/>
+      <c r="H214" s="7"/>
+    </row>
+    <row r="215" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A215" s="16">
         <v>1149587360</v>
       </c>
@@ -6426,10 +6873,12 @@
       <c r="D215" s="19">
         <v>2</v>
       </c>
-      <c r="E215" s="7"/>
-      <c r="F215" s="7"/>
-    </row>
-    <row r="216" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E215" s="27"/>
+      <c r="F215" s="27"/>
+      <c r="G215" s="7"/>
+      <c r="H215" s="7"/>
+    </row>
+    <row r="216" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A216" s="16">
         <v>1149826164</v>
       </c>
@@ -6442,10 +6891,12 @@
       <c r="D216" s="19">
         <v>2</v>
       </c>
-      <c r="E216" s="7"/>
-      <c r="F216" s="7"/>
-    </row>
-    <row r="217" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E216" s="27"/>
+      <c r="F216" s="27"/>
+      <c r="G216" s="7"/>
+      <c r="H216" s="7"/>
+    </row>
+    <row r="217" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A217" s="16">
         <v>2337878892</v>
       </c>
@@ -6458,10 +6909,12 @@
       <c r="D217" s="19">
         <v>2</v>
       </c>
-      <c r="E217" s="7"/>
-      <c r="F217" s="7"/>
-    </row>
-    <row r="218" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E217" s="27"/>
+      <c r="F217" s="27"/>
+      <c r="G217" s="7"/>
+      <c r="H217" s="7"/>
+    </row>
+    <row r="218" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A218" s="18">
         <v>1149207308</v>
       </c>
@@ -6474,10 +6927,12 @@
       <c r="D218" s="22">
         <v>2</v>
       </c>
-      <c r="E218" s="7"/>
-      <c r="F218" s="7"/>
-    </row>
-    <row r="219" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E218" s="27"/>
+      <c r="F218" s="27"/>
+      <c r="G218" s="7"/>
+      <c r="H218" s="7"/>
+    </row>
+    <row r="219" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A219" s="16">
         <v>1147803256</v>
       </c>
@@ -6490,10 +6945,12 @@
       <c r="D219" s="19">
         <v>2</v>
       </c>
-      <c r="E219" s="7"/>
-      <c r="F219" s="7"/>
-    </row>
-    <row r="220" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E219" s="27"/>
+      <c r="F219" s="27"/>
+      <c r="G219" s="7"/>
+      <c r="H219" s="7"/>
+    </row>
+    <row r="220" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A220" s="19">
         <v>1149812065</v>
       </c>
@@ -6506,10 +6963,12 @@
       <c r="D220" s="19">
         <v>3</v>
       </c>
-      <c r="E220" s="7"/>
-      <c r="F220" s="7"/>
-    </row>
-    <row r="221" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E220" s="27"/>
+      <c r="F220" s="27"/>
+      <c r="G220" s="7"/>
+      <c r="H220" s="7"/>
+    </row>
+    <row r="221" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A221" s="19">
         <v>1147392706</v>
       </c>
@@ -6522,10 +6981,12 @@
       <c r="D221" s="19">
         <v>3</v>
       </c>
-      <c r="E221" s="7"/>
-      <c r="F221" s="7"/>
-    </row>
-    <row r="222" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E221" s="27"/>
+      <c r="F221" s="27"/>
+      <c r="G221" s="7"/>
+      <c r="H221" s="7"/>
+    </row>
+    <row r="222" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A222" s="19">
         <v>1145344212</v>
       </c>
@@ -6538,10 +6999,12 @@
       <c r="D222" s="19">
         <v>3</v>
       </c>
-      <c r="E222" s="7"/>
-      <c r="F222" s="7"/>
-    </row>
-    <row r="223" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E222" s="27"/>
+      <c r="F222" s="27"/>
+      <c r="G222" s="7"/>
+      <c r="H222" s="7"/>
+    </row>
+    <row r="223" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A223" s="19">
         <v>1151073234</v>
       </c>
@@ -6554,10 +7017,12 @@
       <c r="D223" s="19">
         <v>3</v>
       </c>
-      <c r="E223" s="7"/>
-      <c r="F223" s="7"/>
-    </row>
-    <row r="224" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E223" s="27"/>
+      <c r="F223" s="27"/>
+      <c r="G223" s="7"/>
+      <c r="H223" s="7"/>
+    </row>
+    <row r="224" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A224" s="19">
         <v>1149661421</v>
       </c>
@@ -6570,10 +7035,12 @@
       <c r="D224" s="19">
         <v>3</v>
       </c>
-      <c r="E224" s="7"/>
-      <c r="F224" s="7"/>
-    </row>
-    <row r="225" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E224" s="27"/>
+      <c r="F224" s="27"/>
+      <c r="G224" s="7"/>
+      <c r="H224" s="7"/>
+    </row>
+    <row r="225" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A225" s="16">
         <v>1147116089</v>
       </c>
@@ -6586,10 +7053,12 @@
       <c r="D225" s="19">
         <v>3</v>
       </c>
-      <c r="E225" s="7"/>
-      <c r="F225" s="7"/>
-    </row>
-    <row r="226" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E225" s="27"/>
+      <c r="F225" s="27"/>
+      <c r="G225" s="7"/>
+      <c r="H225" s="7"/>
+    </row>
+    <row r="226" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A226" s="16">
         <v>1147116014</v>
       </c>
@@ -6602,10 +7071,12 @@
       <c r="D226" s="19">
         <v>3</v>
       </c>
-      <c r="E226" s="7"/>
-      <c r="F226" s="7"/>
-    </row>
-    <row r="227" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E226" s="27"/>
+      <c r="F226" s="27"/>
+      <c r="G226" s="7"/>
+      <c r="H226" s="7"/>
+    </row>
+    <row r="227" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A227" s="16">
         <v>1147138059</v>
       </c>
@@ -6618,10 +7089,12 @@
       <c r="D227" s="19">
         <v>3</v>
       </c>
-      <c r="E227" s="7"/>
-      <c r="F227" s="7"/>
-    </row>
-    <row r="228" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E227" s="27"/>
+      <c r="F227" s="27"/>
+      <c r="G227" s="7"/>
+      <c r="H227" s="7"/>
+    </row>
+    <row r="228" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A228" s="16">
         <v>1146518921</v>
       </c>
@@ -6634,10 +7107,12 @@
       <c r="D228" s="19">
         <v>3</v>
       </c>
-      <c r="E228" s="7"/>
-      <c r="F228" s="7"/>
-    </row>
-    <row r="229" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E228" s="27"/>
+      <c r="F228" s="27"/>
+      <c r="G228" s="7"/>
+      <c r="H228" s="7"/>
+    </row>
+    <row r="229" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A229" s="16">
         <v>1154144388</v>
       </c>
@@ -6650,10 +7125,12 @@
       <c r="D229" s="19">
         <v>3</v>
       </c>
-      <c r="E229" s="7"/>
-      <c r="F229" s="7"/>
-    </row>
-    <row r="230" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E229" s="27"/>
+      <c r="F229" s="27"/>
+      <c r="G229" s="7"/>
+      <c r="H229" s="7"/>
+    </row>
+    <row r="230" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A230" s="16">
         <v>1147117111</v>
       </c>
@@ -6666,10 +7143,12 @@
       <c r="D230" s="19">
         <v>3</v>
       </c>
-      <c r="E230" s="7"/>
-      <c r="F230" s="7"/>
-    </row>
-    <row r="231" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E230" s="27"/>
+      <c r="F230" s="27"/>
+      <c r="G230" s="7"/>
+      <c r="H230" s="7"/>
+    </row>
+    <row r="231" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A231" s="16">
         <v>1147073637</v>
       </c>
@@ -6682,10 +7161,12 @@
       <c r="D231" s="19">
         <v>3</v>
       </c>
-      <c r="E231" s="7"/>
-      <c r="F231" s="7"/>
-    </row>
-    <row r="232" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E231" s="27"/>
+      <c r="F231" s="27"/>
+      <c r="G231" s="7"/>
+      <c r="H231" s="7"/>
+    </row>
+    <row r="232" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A232" s="16">
         <v>1149366534</v>
       </c>
@@ -6698,10 +7179,12 @@
       <c r="D232" s="19">
         <v>3</v>
       </c>
-      <c r="E232" s="7"/>
-      <c r="F232" s="7"/>
-    </row>
-    <row r="233" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E232" s="27"/>
+      <c r="F232" s="27"/>
+      <c r="G232" s="7"/>
+      <c r="H232" s="7"/>
+    </row>
+    <row r="233" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A233" s="16">
         <v>1151122668</v>
       </c>
@@ -6714,10 +7197,12 @@
       <c r="D233" s="19">
         <v>3</v>
       </c>
-      <c r="E233" s="7"/>
-      <c r="F233" s="7"/>
-    </row>
-    <row r="234" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E233" s="27"/>
+      <c r="F233" s="27"/>
+      <c r="G233" s="7"/>
+      <c r="H233" s="7"/>
+    </row>
+    <row r="234" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A234" s="16">
         <v>1147318826</v>
       </c>
@@ -6730,10 +7215,12 @@
       <c r="D234" s="19">
         <v>3</v>
       </c>
-      <c r="E234" s="7"/>
-      <c r="F234" s="7"/>
-    </row>
-    <row r="235" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E234" s="27"/>
+      <c r="F234" s="27"/>
+      <c r="G234" s="7"/>
+      <c r="H234" s="7"/>
+    </row>
+    <row r="235" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A235" s="16">
         <v>2282275516</v>
       </c>
@@ -6746,10 +7233,12 @@
       <c r="D235" s="19">
         <v>3</v>
       </c>
-      <c r="E235" s="7"/>
-      <c r="F235" s="7"/>
-    </row>
-    <row r="236" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E235" s="27"/>
+      <c r="F235" s="27"/>
+      <c r="G235" s="7"/>
+      <c r="H235" s="7"/>
+    </row>
+    <row r="236" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A236" s="16">
         <v>1148331737</v>
       </c>
@@ -6762,10 +7251,12 @@
       <c r="D236" s="19">
         <v>3</v>
       </c>
-      <c r="E236" s="7"/>
-      <c r="F236" s="7"/>
-    </row>
-    <row r="237" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E236" s="27"/>
+      <c r="F236" s="27"/>
+      <c r="G236" s="7"/>
+      <c r="H236" s="7"/>
+    </row>
+    <row r="237" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A237" s="16">
         <v>1148003252</v>
       </c>
@@ -6778,10 +7269,12 @@
       <c r="D237" s="19">
         <v>3</v>
       </c>
-      <c r="E237" s="7"/>
-      <c r="F237" s="7"/>
-    </row>
-    <row r="238" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E237" s="27"/>
+      <c r="F237" s="27"/>
+      <c r="G237" s="7"/>
+      <c r="H237" s="7"/>
+    </row>
+    <row r="238" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A238" s="16">
         <v>1146792161</v>
       </c>
@@ -6794,10 +7287,12 @@
       <c r="D238" s="19">
         <v>3</v>
       </c>
-      <c r="E238" s="7"/>
-      <c r="F238" s="7"/>
-    </row>
-    <row r="239" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E238" s="27"/>
+      <c r="F238" s="27"/>
+      <c r="G238" s="7"/>
+      <c r="H238" s="7"/>
+    </row>
+    <row r="239" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A239" s="16">
         <v>1148196452</v>
       </c>
@@ -6810,10 +7305,12 @@
       <c r="D239" s="19">
         <v>3</v>
       </c>
-      <c r="E239" s="7"/>
-      <c r="F239" s="7"/>
-    </row>
-    <row r="240" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E239" s="27"/>
+      <c r="F239" s="27"/>
+      <c r="G239" s="7"/>
+      <c r="H239" s="7"/>
+    </row>
+    <row r="240" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A240" s="16">
         <v>1146902935</v>
       </c>
@@ -6826,10 +7323,12 @@
       <c r="D240" s="19">
         <v>3</v>
       </c>
-      <c r="E240" s="7"/>
-      <c r="F240" s="7"/>
-    </row>
-    <row r="241" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E240" s="27"/>
+      <c r="F240" s="27"/>
+      <c r="G240" s="7"/>
+      <c r="H240" s="7"/>
+    </row>
+    <row r="241" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A241" s="16">
         <v>1145718209</v>
       </c>
@@ -6842,10 +7341,12 @@
       <c r="D241" s="19">
         <v>3</v>
       </c>
-      <c r="E241" s="7"/>
-      <c r="F241" s="7"/>
-    </row>
-    <row r="242" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E241" s="27"/>
+      <c r="F241" s="27"/>
+      <c r="G241" s="7"/>
+      <c r="H241" s="7"/>
+    </row>
+    <row r="242" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A242" s="16">
         <v>1148921412</v>
       </c>
@@ -6858,10 +7359,12 @@
       <c r="D242" s="19">
         <v>3</v>
       </c>
-      <c r="E242" s="7"/>
-      <c r="F242" s="7"/>
-    </row>
-    <row r="243" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E242" s="27"/>
+      <c r="F242" s="27"/>
+      <c r="G242" s="7"/>
+      <c r="H242" s="7"/>
+    </row>
+    <row r="243" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A243" s="16">
         <v>1150070421</v>
       </c>
@@ -6874,10 +7377,12 @@
       <c r="D243" s="19">
         <v>3</v>
       </c>
-      <c r="E243" s="7"/>
-      <c r="F243" s="7"/>
-    </row>
-    <row r="244" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E243" s="27"/>
+      <c r="F243" s="27"/>
+      <c r="G243" s="7"/>
+      <c r="H243" s="7"/>
+    </row>
+    <row r="244" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A244" s="16">
         <v>1169254040</v>
       </c>
@@ -6890,10 +7395,12 @@
       <c r="D244" s="19">
         <v>3</v>
       </c>
-      <c r="E244" s="7"/>
-      <c r="F244" s="7"/>
-    </row>
-    <row r="245" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E244" s="27"/>
+      <c r="F244" s="27"/>
+      <c r="G244" s="7"/>
+      <c r="H244" s="7"/>
+    </row>
+    <row r="245" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A245" s="16">
         <v>1145733752</v>
       </c>
@@ -6906,10 +7413,12 @@
       <c r="D245" s="19">
         <v>3</v>
       </c>
-      <c r="E245" s="7"/>
-      <c r="F245" s="7"/>
-    </row>
-    <row r="246" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E245" s="27"/>
+      <c r="F245" s="27"/>
+      <c r="G245" s="7"/>
+      <c r="H245" s="7"/>
+    </row>
+    <row r="246" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A246" s="16">
         <v>1146851652</v>
       </c>
@@ -6922,10 +7431,12 @@
       <c r="D246" s="19">
         <v>3</v>
       </c>
-      <c r="E246" s="7"/>
-      <c r="F246" s="7"/>
-    </row>
-    <row r="247" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E246" s="27"/>
+      <c r="F246" s="27"/>
+      <c r="G246" s="7"/>
+      <c r="H246" s="7"/>
+    </row>
+    <row r="247" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A247" s="16">
         <v>1146339948</v>
       </c>
@@ -6938,10 +7449,12 @@
       <c r="D247" s="19">
         <v>4</v>
       </c>
-      <c r="E247" s="7"/>
-      <c r="F247" s="7"/>
-    </row>
-    <row r="248" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E247" s="27"/>
+      <c r="F247" s="27"/>
+      <c r="G247" s="7"/>
+      <c r="H247" s="7"/>
+    </row>
+    <row r="248" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A248" s="16">
         <v>1156163931</v>
       </c>
@@ -6954,10 +7467,12 @@
       <c r="D248" s="19">
         <v>4</v>
       </c>
-      <c r="E248" s="7"/>
-      <c r="F248" s="7"/>
-    </row>
-    <row r="249" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E248" s="27"/>
+      <c r="F248" s="27"/>
+      <c r="G248" s="7"/>
+      <c r="H248" s="7"/>
+    </row>
+    <row r="249" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A249" s="16">
         <v>1148066275</v>
       </c>
@@ -6970,10 +7485,12 @@
       <c r="D249" s="19">
         <v>4</v>
       </c>
-      <c r="E249" s="7"/>
-      <c r="F249" s="7"/>
-    </row>
-    <row r="250" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E249" s="27"/>
+      <c r="F249" s="27"/>
+      <c r="G249" s="7"/>
+      <c r="H249" s="7"/>
+    </row>
+    <row r="250" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A250" s="16">
         <v>1148850710</v>
       </c>
@@ -6986,10 +7503,12 @@
       <c r="D250" s="19">
         <v>4</v>
       </c>
-      <c r="E250" s="7"/>
-      <c r="F250" s="7"/>
-    </row>
-    <row r="251" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E250" s="27"/>
+      <c r="F250" s="27"/>
+      <c r="G250" s="7"/>
+      <c r="H250" s="7"/>
+    </row>
+    <row r="251" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A251" s="16">
         <v>1146399652</v>
       </c>
@@ -7002,10 +7521,12 @@
       <c r="D251" s="19">
         <v>4</v>
       </c>
-      <c r="E251" s="7"/>
-      <c r="F251" s="7"/>
-    </row>
-    <row r="252" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E251" s="27"/>
+      <c r="F251" s="27"/>
+      <c r="G251" s="7"/>
+      <c r="H251" s="7"/>
+    </row>
+    <row r="252" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A252" s="16">
         <v>1148398181</v>
       </c>
@@ -7018,10 +7539,12 @@
       <c r="D252" s="19">
         <v>4</v>
       </c>
-      <c r="E252" s="7"/>
-      <c r="F252" s="7"/>
-    </row>
-    <row r="253" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E252" s="27"/>
+      <c r="F252" s="27"/>
+      <c r="G252" s="7"/>
+      <c r="H252" s="7"/>
+    </row>
+    <row r="253" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A253" s="16">
         <v>1145648166</v>
       </c>
@@ -7034,10 +7557,12 @@
       <c r="D253" s="19">
         <v>4</v>
       </c>
-      <c r="E253" s="7"/>
-      <c r="F253" s="7"/>
-    </row>
-    <row r="254" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E253" s="27"/>
+      <c r="F253" s="27"/>
+      <c r="G253" s="7"/>
+      <c r="H253" s="7"/>
+    </row>
+    <row r="254" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A254" s="16">
         <v>1147594236</v>
       </c>
@@ -7050,10 +7575,12 @@
       <c r="D254" s="19">
         <v>4</v>
       </c>
-      <c r="E254" s="7"/>
-      <c r="F254" s="7"/>
-    </row>
-    <row r="255" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E254" s="27"/>
+      <c r="F254" s="27"/>
+      <c r="G254" s="7"/>
+      <c r="H254" s="7"/>
+    </row>
+    <row r="255" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A255" s="16">
         <v>1146766389</v>
       </c>
@@ -7066,10 +7593,12 @@
       <c r="D255" s="19">
         <v>4</v>
       </c>
-      <c r="E255" s="7"/>
-      <c r="F255" s="7"/>
-    </row>
-    <row r="256" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E255" s="27"/>
+      <c r="F255" s="27"/>
+      <c r="G255" s="7"/>
+      <c r="H255" s="7"/>
+    </row>
+    <row r="256" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A256" s="16">
         <v>1148766015</v>
       </c>
@@ -7082,10 +7611,12 @@
       <c r="D256" s="19">
         <v>4</v>
       </c>
-      <c r="E256" s="7"/>
-      <c r="F256" s="7"/>
-    </row>
-    <row r="257" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E256" s="27"/>
+      <c r="F256" s="27"/>
+      <c r="G256" s="7"/>
+      <c r="H256" s="7"/>
+    </row>
+    <row r="257" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A257" s="16">
         <v>1161794449</v>
       </c>
@@ -7098,10 +7629,12 @@
       <c r="D257" s="19">
         <v>4</v>
       </c>
-      <c r="E257" s="7"/>
-      <c r="F257" s="7"/>
-    </row>
-    <row r="258" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E257" s="27"/>
+      <c r="F257" s="27"/>
+      <c r="G257" s="7"/>
+      <c r="H257" s="7"/>
+    </row>
+    <row r="258" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A258" s="16">
         <v>1149400937</v>
       </c>
@@ -7114,10 +7647,12 @@
       <c r="D258" s="19">
         <v>4</v>
       </c>
-      <c r="E258" s="7"/>
-      <c r="F258" s="7"/>
-    </row>
-    <row r="259" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E258" s="27"/>
+      <c r="F258" s="27"/>
+      <c r="G258" s="7"/>
+      <c r="H258" s="7"/>
+    </row>
+    <row r="259" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A259" s="16">
         <v>1148097148</v>
       </c>
@@ -7130,10 +7665,12 @@
       <c r="D259" s="19">
         <v>4</v>
       </c>
-      <c r="E259" s="7"/>
-      <c r="F259" s="7"/>
-    </row>
-    <row r="260" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E259" s="27"/>
+      <c r="F259" s="27"/>
+      <c r="G259" s="7"/>
+      <c r="H259" s="7"/>
+    </row>
+    <row r="260" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A260" s="16">
         <v>1149512558</v>
       </c>
@@ -7146,10 +7683,12 @@
       <c r="D260" s="19">
         <v>4</v>
       </c>
-      <c r="E260" s="7"/>
-      <c r="F260" s="7"/>
-    </row>
-    <row r="261" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E260" s="27"/>
+      <c r="F260" s="27"/>
+      <c r="G260" s="7"/>
+      <c r="H260" s="7"/>
+    </row>
+    <row r="261" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A261" s="16">
         <v>1148636135</v>
       </c>
@@ -7162,10 +7701,12 @@
       <c r="D261" s="19">
         <v>4</v>
       </c>
-      <c r="E261" s="7"/>
-      <c r="F261" s="7"/>
-    </row>
-    <row r="262" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E261" s="27"/>
+      <c r="F261" s="27"/>
+      <c r="G261" s="7"/>
+      <c r="H261" s="7"/>
+    </row>
+    <row r="262" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A262" s="16">
         <v>1148833708</v>
       </c>
@@ -7178,10 +7719,12 @@
       <c r="D262" s="19">
         <v>4</v>
       </c>
-      <c r="E262" s="7"/>
-      <c r="F262" s="7"/>
-    </row>
-    <row r="263" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E262" s="27"/>
+      <c r="F262" s="27"/>
+      <c r="G262" s="7"/>
+      <c r="H262" s="7"/>
+    </row>
+    <row r="263" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A263" s="16">
         <v>1145244214</v>
       </c>
@@ -7194,10 +7737,12 @@
       <c r="D263" s="19">
         <v>4</v>
       </c>
-      <c r="E263" s="7"/>
-      <c r="F263" s="7"/>
-    </row>
-    <row r="264" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E263" s="27"/>
+      <c r="F263" s="27"/>
+      <c r="G263" s="7"/>
+      <c r="H263" s="7"/>
+    </row>
+    <row r="264" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A264" s="16">
         <v>1149415935</v>
       </c>
@@ -7210,10 +7755,12 @@
       <c r="D264" s="19">
         <v>4</v>
       </c>
-      <c r="E264" s="7"/>
-      <c r="F264" s="7"/>
-    </row>
-    <row r="265" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E264" s="27"/>
+      <c r="F264" s="27"/>
+      <c r="G264" s="7"/>
+      <c r="H264" s="7"/>
+    </row>
+    <row r="265" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A265" s="16">
         <v>2282843446</v>
       </c>
@@ -7226,10 +7773,12 @@
       <c r="D265" s="19">
         <v>4</v>
       </c>
-      <c r="E265" s="7"/>
-      <c r="F265" s="7"/>
-    </row>
-    <row r="266" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E265" s="27"/>
+      <c r="F265" s="27"/>
+      <c r="G265" s="7"/>
+      <c r="H265" s="7"/>
+    </row>
+    <row r="266" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A266" s="16">
         <v>1147952509</v>
       </c>
@@ -7242,10 +7791,12 @@
       <c r="D266" s="19">
         <v>4</v>
       </c>
-      <c r="E266" s="7"/>
-      <c r="F266" s="7"/>
-    </row>
-    <row r="267" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E266" s="27"/>
+      <c r="F266" s="27"/>
+      <c r="G266" s="7"/>
+      <c r="H266" s="7"/>
+    </row>
+    <row r="267" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A267" s="16">
         <v>1149342303</v>
       </c>
@@ -7258,10 +7809,12 @@
       <c r="D267" s="19">
         <v>4</v>
       </c>
-      <c r="E267" s="7"/>
-      <c r="F267" s="7"/>
-    </row>
-    <row r="268" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E267" s="27"/>
+      <c r="F267" s="27"/>
+      <c r="G267" s="7"/>
+      <c r="H267" s="7"/>
+    </row>
+    <row r="268" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A268" s="16">
         <v>1147346579</v>
       </c>
@@ -7274,10 +7827,12 @@
       <c r="D268" s="19">
         <v>4</v>
       </c>
-      <c r="E268" s="7"/>
-      <c r="F268" s="7"/>
-    </row>
-    <row r="269" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E268" s="27"/>
+      <c r="F268" s="27"/>
+      <c r="G268" s="7"/>
+      <c r="H268" s="7"/>
+    </row>
+    <row r="269" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A269" s="16">
         <v>1146982663</v>
       </c>
@@ -7290,10 +7845,12 @@
       <c r="D269" s="19">
         <v>4</v>
       </c>
-      <c r="E269" s="7"/>
-      <c r="F269" s="7"/>
-    </row>
-    <row r="270" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E269" s="27"/>
+      <c r="F269" s="27"/>
+      <c r="G269" s="7"/>
+      <c r="H269" s="7"/>
+    </row>
+    <row r="270" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A270" s="16">
         <v>1148895673</v>
       </c>
@@ -7306,10 +7863,12 @@
       <c r="D270" s="19">
         <v>4</v>
       </c>
-      <c r="E270" s="7"/>
-      <c r="F270" s="7"/>
-    </row>
-    <row r="271" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E270" s="27"/>
+      <c r="F270" s="27"/>
+      <c r="G270" s="7"/>
+      <c r="H270" s="7"/>
+    </row>
+    <row r="271" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A271" s="16">
         <v>1147817827</v>
       </c>
@@ -7322,10 +7881,12 @@
       <c r="D271" s="19">
         <v>4</v>
       </c>
-      <c r="E271" s="7"/>
-      <c r="F271" s="7"/>
-    </row>
-    <row r="272" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E271" s="27"/>
+      <c r="F271" s="27"/>
+      <c r="G271" s="7"/>
+      <c r="H271" s="7"/>
+    </row>
+    <row r="272" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A272" s="16">
         <v>2317822274</v>
       </c>
@@ -7338,10 +7899,12 @@
       <c r="D272" s="19">
         <v>5</v>
       </c>
-      <c r="E272" s="7"/>
-      <c r="F272" s="7"/>
-    </row>
-    <row r="273" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E272" s="27"/>
+      <c r="F272" s="27"/>
+      <c r="G272" s="7"/>
+      <c r="H272" s="7"/>
+    </row>
+    <row r="273" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A273" s="16">
         <v>2368543738</v>
       </c>
@@ -7354,10 +7917,12 @@
       <c r="D273" s="19">
         <v>5</v>
       </c>
-      <c r="E273" s="7"/>
-      <c r="F273" s="7"/>
-    </row>
-    <row r="274" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E273" s="27"/>
+      <c r="F273" s="27"/>
+      <c r="G273" s="7"/>
+      <c r="H273" s="7"/>
+    </row>
+    <row r="274" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A274" s="16">
         <v>1147244998</v>
       </c>
@@ -7370,10 +7935,12 @@
       <c r="D274" s="19">
         <v>5</v>
       </c>
-      <c r="E274" s="7"/>
-      <c r="F274" s="7"/>
-    </row>
-    <row r="275" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E274" s="27"/>
+      <c r="F274" s="27"/>
+      <c r="G274" s="7"/>
+      <c r="H274" s="7"/>
+    </row>
+    <row r="275" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A275" s="16">
         <v>1147138414</v>
       </c>
@@ -7386,10 +7953,12 @@
       <c r="D275" s="19">
         <v>5</v>
       </c>
-      <c r="E275" s="7"/>
-      <c r="F275" s="7"/>
-    </row>
-    <row r="276" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E275" s="27"/>
+      <c r="F275" s="27"/>
+      <c r="G275" s="7"/>
+      <c r="H275" s="7"/>
+    </row>
+    <row r="276" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A276" s="16">
         <v>1147800385</v>
       </c>
@@ -7402,10 +7971,12 @@
       <c r="D276" s="19">
         <v>5</v>
       </c>
-      <c r="E276" s="7"/>
-      <c r="F276" s="7"/>
-    </row>
-    <row r="277" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E276" s="27"/>
+      <c r="F276" s="27"/>
+      <c r="G276" s="7"/>
+      <c r="H276" s="7"/>
+    </row>
+    <row r="277" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A277" s="16">
         <v>1145124374</v>
       </c>
@@ -7418,10 +7989,12 @@
       <c r="D277" s="19">
         <v>5</v>
       </c>
-      <c r="E277" s="7"/>
-      <c r="F277" s="7"/>
-    </row>
-    <row r="278" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E277" s="27"/>
+      <c r="F277" s="27"/>
+      <c r="G277" s="7"/>
+      <c r="H277" s="7"/>
+    </row>
+    <row r="278" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A278" s="16">
         <v>1146362445</v>
       </c>
@@ -7434,10 +8007,12 @@
       <c r="D278" s="19">
         <v>5</v>
       </c>
-      <c r="E278" s="7"/>
-      <c r="F278" s="7"/>
-    </row>
-    <row r="279" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E278" s="27"/>
+      <c r="F278" s="27"/>
+      <c r="G278" s="7"/>
+      <c r="H278" s="7"/>
+    </row>
+    <row r="279" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A279" s="16">
         <v>1149064972</v>
       </c>
@@ -7450,10 +8025,12 @@
       <c r="D279" s="19">
         <v>5</v>
       </c>
-      <c r="E279" s="7"/>
-      <c r="F279" s="7"/>
-    </row>
-    <row r="280" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E279" s="27"/>
+      <c r="F279" s="27"/>
+      <c r="G279" s="7"/>
+      <c r="H279" s="7"/>
+    </row>
+    <row r="280" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A280" s="16">
         <v>1146726300</v>
       </c>
@@ -7466,10 +8043,12 @@
       <c r="D280" s="19">
         <v>5</v>
       </c>
-      <c r="E280" s="7"/>
-      <c r="F280" s="7"/>
-    </row>
-    <row r="281" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E280" s="27"/>
+      <c r="F280" s="27"/>
+      <c r="G280" s="7"/>
+      <c r="H280" s="7"/>
+    </row>
+    <row r="281" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A281" s="16">
         <v>1149452821</v>
       </c>
@@ -7482,10 +8061,12 @@
       <c r="D281" s="19">
         <v>5</v>
       </c>
-      <c r="E281" s="7"/>
-      <c r="F281" s="7"/>
-    </row>
-    <row r="282" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E281" s="27"/>
+      <c r="F281" s="27"/>
+      <c r="G281" s="7"/>
+      <c r="H281" s="7"/>
+    </row>
+    <row r="282" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A282" s="16">
         <v>1146907470</v>
       </c>
@@ -7498,10 +8079,12 @@
       <c r="D282" s="19">
         <v>5</v>
       </c>
-      <c r="E282" s="7"/>
-      <c r="F282" s="7"/>
-    </row>
-    <row r="283" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E282" s="27"/>
+      <c r="F282" s="27"/>
+      <c r="G282" s="7"/>
+      <c r="H282" s="7"/>
+    </row>
+    <row r="283" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A283" s="16">
         <v>1145545081</v>
       </c>
@@ -7514,10 +8097,12 @@
       <c r="D283" s="19">
         <v>5</v>
       </c>
-      <c r="E283" s="7"/>
-      <c r="F283" s="7"/>
-    </row>
-    <row r="284" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E283" s="27"/>
+      <c r="F283" s="27"/>
+      <c r="G283" s="7"/>
+      <c r="H283" s="7"/>
+    </row>
+    <row r="284" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A284" s="16">
         <v>1149931006</v>
       </c>
@@ -7530,10 +8115,12 @@
       <c r="D284" s="19">
         <v>5</v>
       </c>
-      <c r="E284" s="7"/>
-      <c r="F284" s="7"/>
-    </row>
-    <row r="285" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E284" s="27"/>
+      <c r="F284" s="27"/>
+      <c r="G284" s="7"/>
+      <c r="H284" s="7"/>
+    </row>
+    <row r="285" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A285" s="16">
         <v>2277240962</v>
       </c>
@@ -7546,10 +8133,12 @@
       <c r="D285" s="19">
         <v>5</v>
       </c>
-      <c r="E285" s="7"/>
-      <c r="F285" s="7"/>
-    </row>
-    <row r="286" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E285" s="27"/>
+      <c r="F285" s="27"/>
+      <c r="G285" s="7"/>
+      <c r="H285" s="7"/>
+    </row>
+    <row r="286" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A286" s="16">
         <v>1145922330</v>
       </c>
@@ -7562,10 +8151,12 @@
       <c r="D286" s="19">
         <v>5</v>
       </c>
-      <c r="E286" s="7"/>
-      <c r="F286" s="7"/>
-    </row>
-    <row r="287" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E286" s="27"/>
+      <c r="F286" s="27"/>
+      <c r="G286" s="7"/>
+      <c r="H286" s="7"/>
+    </row>
+    <row r="287" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A287" s="16">
         <v>1168345146</v>
       </c>
@@ -7578,10 +8169,12 @@
       <c r="D287" s="19">
         <v>5</v>
       </c>
-      <c r="E287" s="7"/>
-      <c r="F287" s="7"/>
-    </row>
-    <row r="288" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E287" s="27"/>
+      <c r="F287" s="27"/>
+      <c r="G287" s="7"/>
+      <c r="H287" s="7"/>
+    </row>
+    <row r="288" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A288" s="16">
         <v>2395502558</v>
       </c>
@@ -7594,10 +8187,12 @@
       <c r="D288" s="19">
         <v>5</v>
       </c>
-      <c r="E288" s="7"/>
-      <c r="F288" s="7"/>
-    </row>
-    <row r="289" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E288" s="27"/>
+      <c r="F288" s="27"/>
+      <c r="G288" s="7"/>
+      <c r="H288" s="7"/>
+    </row>
+    <row r="289" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A289" s="16">
         <v>1146162415</v>
       </c>
@@ -7610,10 +8205,12 @@
       <c r="D289" s="19">
         <v>5</v>
       </c>
-      <c r="E289" s="7"/>
-      <c r="F289" s="7"/>
-    </row>
-    <row r="290" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E289" s="27"/>
+      <c r="F289" s="27"/>
+      <c r="G289" s="7"/>
+      <c r="H289" s="7"/>
+    </row>
+    <row r="290" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A290" s="16">
         <v>1152946875</v>
       </c>
@@ -7626,10 +8223,12 @@
       <c r="D290" s="19">
         <v>5</v>
       </c>
-      <c r="E290" s="7"/>
-      <c r="F290" s="7"/>
-    </row>
-    <row r="291" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E290" s="27"/>
+      <c r="F290" s="27"/>
+      <c r="G290" s="7"/>
+      <c r="H290" s="7"/>
+    </row>
+    <row r="291" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A291" s="16">
         <v>1150772208</v>
       </c>
@@ -7642,10 +8241,12 @@
       <c r="D291" s="19">
         <v>5</v>
       </c>
-      <c r="E291" s="7"/>
-      <c r="F291" s="7"/>
-    </row>
-    <row r="292" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E291" s="27"/>
+      <c r="F291" s="27"/>
+      <c r="G291" s="7"/>
+      <c r="H291" s="7"/>
+    </row>
+    <row r="292" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A292" s="16">
         <v>1148980897</v>
       </c>
@@ -7658,8 +8259,10 @@
       <c r="D292" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="293" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E292" s="27"/>
+      <c r="F292" s="27"/>
+    </row>
+    <row r="293" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A293" s="16">
         <v>1146607773</v>
       </c>
@@ -7672,8 +8275,10 @@
       <c r="D293" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="294" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E293" s="27"/>
+      <c r="F293" s="27"/>
+    </row>
+    <row r="294" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A294" s="16">
         <v>1146979255</v>
       </c>
@@ -7686,8 +8291,10 @@
       <c r="D294" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="295" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E294" s="27"/>
+      <c r="F294" s="27"/>
+    </row>
+    <row r="295" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A295" s="16">
         <v>1149811893</v>
       </c>
@@ -7700,8 +8307,10 @@
       <c r="D295" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="296" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E295" s="27"/>
+      <c r="F295" s="27"/>
+    </row>
+    <row r="296" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A296" s="16">
         <v>1149339077</v>
       </c>
@@ -7714,8 +8323,10 @@
       <c r="D296" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="297" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E296" s="27"/>
+      <c r="F296" s="27"/>
+    </row>
+    <row r="297" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A297" s="16">
         <v>1149508598</v>
       </c>
@@ -7728,8 +8339,10 @@
       <c r="D297" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="298" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E297" s="27"/>
+      <c r="F297" s="27"/>
+    </row>
+    <row r="298" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A298" s="16">
         <v>1147789356</v>
       </c>
@@ -7742,8 +8355,10 @@
       <c r="D298" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="299" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E298" s="27"/>
+      <c r="F298" s="27"/>
+    </row>
+    <row r="299" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A299" s="16">
         <v>1146611726</v>
       </c>
@@ -7756,8 +8371,10 @@
       <c r="D299" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="300" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E299" s="27"/>
+      <c r="F299" s="27"/>
+    </row>
+    <row r="300" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A300" s="16">
         <v>1147262016</v>
       </c>
@@ -7770,8 +8387,10 @@
       <c r="D300" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="301" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E300" s="27"/>
+      <c r="F300" s="27"/>
+    </row>
+    <row r="301" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A301" s="16">
         <v>1147494130</v>
       </c>
@@ -7784,8 +8403,10 @@
       <c r="D301" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="302" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E301" s="27"/>
+      <c r="F301" s="27"/>
+    </row>
+    <row r="302" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A302" s="16">
         <v>1148272907</v>
       </c>
@@ -7798,8 +8419,10 @@
       <c r="D302" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="303" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E302" s="27"/>
+      <c r="F302" s="27"/>
+    </row>
+    <row r="303" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A303" s="16">
         <v>1149254607</v>
       </c>
@@ -7812,8 +8435,10 @@
       <c r="D303" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="304" spans="1:6" ht="19" customHeight="1" thickBot="1">
+      <c r="E303" s="27"/>
+      <c r="F303" s="27"/>
+    </row>
+    <row r="304" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A304" s="16">
         <v>1149049734</v>
       </c>
@@ -7826,8 +8451,10 @@
       <c r="D304" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="305" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E304" s="27"/>
+      <c r="F304" s="27"/>
+    </row>
+    <row r="305" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A305" s="16">
         <v>1147396244</v>
       </c>
@@ -7840,8 +8467,10 @@
       <c r="D305" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="306" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E305" s="27"/>
+      <c r="F305" s="27"/>
+    </row>
+    <row r="306" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A306" s="16">
         <v>1146310931</v>
       </c>
@@ -7854,8 +8483,10 @@
       <c r="D306" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="307" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E306" s="27"/>
+      <c r="F306" s="27"/>
+    </row>
+    <row r="307" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A307" s="16">
         <v>1145927230</v>
       </c>
@@ -7868,8 +8499,10 @@
       <c r="D307" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="308" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E307" s="27"/>
+      <c r="F307" s="27"/>
+    </row>
+    <row r="308" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A308" s="16">
         <v>1148274754</v>
       </c>
@@ -7882,8 +8515,10 @@
       <c r="D308" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="309" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E308" s="27"/>
+      <c r="F308" s="27"/>
+    </row>
+    <row r="309" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A309" s="16">
         <v>1147544322</v>
       </c>
@@ -7896,8 +8531,10 @@
       <c r="D309" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="310" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E309" s="27"/>
+      <c r="F309" s="27"/>
+    </row>
+    <row r="310" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A310" s="16">
         <v>1146374598</v>
       </c>
@@ -7910,8 +8547,10 @@
       <c r="D310" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="311" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E310" s="27"/>
+      <c r="F310" s="27"/>
+    </row>
+    <row r="311" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A311" s="16">
         <v>1150177127</v>
       </c>
@@ -7924,8 +8563,10 @@
       <c r="D311" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="312" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E311" s="27"/>
+      <c r="F311" s="27"/>
+    </row>
+    <row r="312" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A312" s="16">
         <v>1147539728</v>
       </c>
@@ -7938,8 +8579,10 @@
       <c r="D312" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="313" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E312" s="27"/>
+      <c r="F312" s="27"/>
+    </row>
+    <row r="313" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A313" s="16">
         <v>1147293839</v>
       </c>
@@ -7952,8 +8595,10 @@
       <c r="D313" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="314" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E313" s="27"/>
+      <c r="F313" s="27"/>
+    </row>
+    <row r="314" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A314" s="16">
         <v>1148251356</v>
       </c>
@@ -7966,8 +8611,10 @@
       <c r="D314" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="315" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E314" s="27"/>
+      <c r="F314" s="27"/>
+    </row>
+    <row r="315" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A315" s="16">
         <v>1147637472</v>
       </c>
@@ -7980,8 +8627,10 @@
       <c r="D315" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="316" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E315" s="27"/>
+      <c r="F315" s="27"/>
+    </row>
+    <row r="316" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A316" s="16">
         <v>1149530295</v>
       </c>
@@ -7994,8 +8643,10 @@
       <c r="D316" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="317" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E316" s="27"/>
+      <c r="F316" s="27"/>
+    </row>
+    <row r="317" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A317" s="16">
         <v>1148778382</v>
       </c>
@@ -8008,8 +8659,10 @@
       <c r="D317" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="318" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E317" s="27"/>
+      <c r="F317" s="27"/>
+    </row>
+    <row r="318" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A318" s="16">
         <v>1147236846</v>
       </c>
@@ -8022,8 +8675,10 @@
       <c r="D318" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="319" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E318" s="27"/>
+      <c r="F318" s="27"/>
+    </row>
+    <row r="319" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A319" s="16">
         <v>2389352689</v>
       </c>
@@ -8036,8 +8691,10 @@
       <c r="D319" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="320" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E319" s="27"/>
+      <c r="F319" s="27"/>
+    </row>
+    <row r="320" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A320" s="16">
         <v>2319640955</v>
       </c>
@@ -8050,8 +8707,10 @@
       <c r="D320" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="321" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E320" s="27"/>
+      <c r="F320" s="27"/>
+    </row>
+    <row r="321" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A321" s="16">
         <v>1141627537</v>
       </c>
@@ -8064,8 +8723,10 @@
       <c r="D321" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="322" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E321" s="27"/>
+      <c r="F321" s="27"/>
+    </row>
+    <row r="322" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A322" s="16">
         <v>1164194308</v>
       </c>
@@ -8078,8 +8739,10 @@
       <c r="D322" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="323" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E322" s="27"/>
+      <c r="F322" s="27"/>
+    </row>
+    <row r="323" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A323" s="16">
         <v>1144571658</v>
       </c>
@@ -8092,8 +8755,10 @@
       <c r="D323" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="324" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E323" s="27"/>
+      <c r="F323" s="27"/>
+    </row>
+    <row r="324" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A324" s="16">
         <v>1146016231</v>
       </c>
@@ -8106,8 +8771,10 @@
       <c r="D324" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="325" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E324" s="27"/>
+      <c r="F324" s="27"/>
+    </row>
+    <row r="325" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A325" s="16">
         <v>1146658867</v>
       </c>
@@ -8120,8 +8787,10 @@
       <c r="D325" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="326" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E325" s="27"/>
+      <c r="F325" s="27"/>
+    </row>
+    <row r="326" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A326" s="16">
         <v>1142495868</v>
       </c>
@@ -8134,8 +8803,10 @@
       <c r="D326" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="327" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E326" s="27"/>
+      <c r="F326" s="27"/>
+    </row>
+    <row r="327" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A327" s="16">
         <v>1144709803</v>
       </c>
@@ -8148,8 +8819,10 @@
       <c r="D327" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="328" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E327" s="27"/>
+      <c r="F327" s="27"/>
+    </row>
+    <row r="328" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A328" s="16">
         <v>1142279023</v>
       </c>
@@ -8162,8 +8835,10 @@
       <c r="D328" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="329" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E328" s="27"/>
+      <c r="F328" s="27"/>
+    </row>
+    <row r="329" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A329" s="16">
         <v>1144228549</v>
       </c>
@@ -8176,8 +8851,10 @@
       <c r="D329" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="330" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E329" s="27"/>
+      <c r="F329" s="27"/>
+    </row>
+    <row r="330" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A330" s="16">
         <v>1146325665</v>
       </c>
@@ -8190,8 +8867,10 @@
       <c r="D330" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="331" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E330" s="27"/>
+      <c r="F330" s="27"/>
+    </row>
+    <row r="331" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A331" s="16">
         <v>1142362704</v>
       </c>
@@ -8204,8 +8883,10 @@
       <c r="D331" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="332" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E331" s="27"/>
+      <c r="F331" s="27"/>
+    </row>
+    <row r="332" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A332" s="16">
         <v>2405032851</v>
       </c>
@@ -8218,8 +8899,10 @@
       <c r="D332" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="333" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E332" s="27"/>
+      <c r="F332" s="27"/>
+    </row>
+    <row r="333" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A333" s="16">
         <v>1143136982</v>
       </c>
@@ -8232,8 +8915,10 @@
       <c r="D333" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="334" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E333" s="27"/>
+      <c r="F333" s="27"/>
+    </row>
+    <row r="334" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A334" s="16">
         <v>1144780952</v>
       </c>
@@ -8246,8 +8931,10 @@
       <c r="D334" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="335" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E334" s="27"/>
+      <c r="F334" s="27"/>
+    </row>
+    <row r="335" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A335" s="16">
         <v>2438353423</v>
       </c>
@@ -8260,8 +8947,10 @@
       <c r="D335" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="336" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E335" s="27"/>
+      <c r="F335" s="27"/>
+    </row>
+    <row r="336" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A336" s="16">
         <v>2280411113</v>
       </c>
@@ -8274,8 +8963,10 @@
       <c r="D336" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="337" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E336" s="27"/>
+      <c r="F336" s="27"/>
+    </row>
+    <row r="337" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A337" s="16">
         <v>1146016322</v>
       </c>
@@ -8288,8 +8979,10 @@
       <c r="D337" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="338" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E337" s="27"/>
+      <c r="F337" s="27"/>
+    </row>
+    <row r="338" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A338" s="16">
         <v>1144674031</v>
       </c>
@@ -8302,8 +8995,10 @@
       <c r="D338" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="339" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E338" s="27"/>
+      <c r="F338" s="27"/>
+    </row>
+    <row r="339" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A339" s="16">
         <v>1145086698</v>
       </c>
@@ -8316,8 +9011,10 @@
       <c r="D339" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="340" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E339" s="27"/>
+      <c r="F339" s="27"/>
+    </row>
+    <row r="340" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A340" s="16">
         <v>1144494901</v>
       </c>
@@ -8330,8 +9027,10 @@
       <c r="D340" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="341" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E340" s="27"/>
+      <c r="F340" s="27"/>
+    </row>
+    <row r="341" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A341" s="16">
         <v>1144188545</v>
       </c>
@@ -8344,8 +9043,10 @@
       <c r="D341" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="342" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E341" s="27"/>
+      <c r="F341" s="27"/>
+    </row>
+    <row r="342" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A342" s="16">
         <v>2266962568</v>
       </c>
@@ -8358,8 +9059,10 @@
       <c r="D342" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="343" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E342" s="27"/>
+      <c r="F342" s="27"/>
+    </row>
+    <row r="343" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A343" s="16">
         <v>1153696263</v>
       </c>
@@ -8372,8 +9075,10 @@
       <c r="D343" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="344" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E343" s="27"/>
+      <c r="F343" s="27"/>
+    </row>
+    <row r="344" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A344" s="16">
         <v>2529355154</v>
       </c>
@@ -8386,8 +9091,10 @@
       <c r="D344" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="345" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E344" s="27"/>
+      <c r="F344" s="27"/>
+    </row>
+    <row r="345" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A345" s="16">
         <v>1143099396</v>
       </c>
@@ -8400,8 +9107,10 @@
       <c r="D345" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="346" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E345" s="27"/>
+      <c r="F345" s="27"/>
+    </row>
+    <row r="346" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A346" s="16">
         <v>1143641072</v>
       </c>
@@ -8414,8 +9123,10 @@
       <c r="D346" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="347" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E346" s="27"/>
+      <c r="F346" s="27"/>
+    </row>
+    <row r="347" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A347" s="16">
         <v>2267767933</v>
       </c>
@@ -8428,8 +9139,10 @@
       <c r="D347" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="348" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E347" s="27"/>
+      <c r="F347" s="27"/>
+    </row>
+    <row r="348" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A348" s="16">
         <v>1144982103</v>
       </c>
@@ -8442,8 +9155,10 @@
       <c r="D348" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="349" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E348" s="27"/>
+      <c r="F348" s="27"/>
+    </row>
+    <row r="349" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A349" s="16">
         <v>1145324693</v>
       </c>
@@ -8456,8 +9171,10 @@
       <c r="D349" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="350" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E349" s="27"/>
+      <c r="F349" s="27"/>
+    </row>
+    <row r="350" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A350" s="16">
         <v>1145507560</v>
       </c>
@@ -8470,8 +9187,10 @@
       <c r="D350" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="351" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E350" s="27"/>
+      <c r="F350" s="27"/>
+    </row>
+    <row r="351" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A351" s="16">
         <v>1144568779</v>
       </c>
@@ -8484,8 +9203,10 @@
       <c r="D351" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="352" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E351" s="27"/>
+      <c r="F351" s="27"/>
+    </row>
+    <row r="352" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A352" s="16">
         <v>1145420848</v>
       </c>
@@ -8498,8 +9219,10 @@
       <c r="D352" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="353" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E352" s="27"/>
+      <c r="F352" s="27"/>
+    </row>
+    <row r="353" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A353" s="16">
         <v>2266115928</v>
       </c>
@@ -8512,8 +9235,10 @@
       <c r="D353" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="354" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E353" s="27"/>
+      <c r="F353" s="27"/>
+    </row>
+    <row r="354" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A354" s="16">
         <v>1165441120</v>
       </c>
@@ -8526,8 +9251,10 @@
       <c r="D354" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="355" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E354" s="27"/>
+      <c r="F354" s="27"/>
+    </row>
+    <row r="355" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A355" s="16">
         <v>1142620572</v>
       </c>
@@ -8540,8 +9267,10 @@
       <c r="D355" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="356" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E355" s="27"/>
+      <c r="F355" s="27"/>
+    </row>
+    <row r="356" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A356" s="16">
         <v>1153501638</v>
       </c>
@@ -8554,8 +9283,10 @@
       <c r="D356" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="357" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E356" s="27"/>
+      <c r="F356" s="27"/>
+    </row>
+    <row r="357" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A357" s="16">
         <v>1144039276</v>
       </c>
@@ -8568,8 +9299,10 @@
       <c r="D357" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="358" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E357" s="27"/>
+      <c r="F357" s="27"/>
+    </row>
+    <row r="358" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A358" s="16">
         <v>2261820829</v>
       </c>
@@ -8582,8 +9315,10 @@
       <c r="D358" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="359" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E358" s="27"/>
+      <c r="F358" s="27"/>
+    </row>
+    <row r="359" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A359" s="16">
         <v>1156658526</v>
       </c>
@@ -8596,8 +9331,10 @@
       <c r="D359" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="360" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E359" s="27"/>
+      <c r="F359" s="27"/>
+    </row>
+    <row r="360" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A360" s="16">
         <v>1141650042</v>
       </c>
@@ -8610,8 +9347,10 @@
       <c r="D360" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="361" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E360" s="27"/>
+      <c r="F360" s="27"/>
+    </row>
+    <row r="361" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A361" s="16">
         <v>1143410536</v>
       </c>
@@ -8624,8 +9363,10 @@
       <c r="D361" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="362" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E361" s="27"/>
+      <c r="F361" s="27"/>
+    </row>
+    <row r="362" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A362" s="16">
         <v>1144769229</v>
       </c>
@@ -8638,8 +9379,10 @@
       <c r="D362" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="363" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E362" s="27"/>
+      <c r="F362" s="27"/>
+    </row>
+    <row r="363" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A363" s="16">
         <v>1145161178</v>
       </c>
@@ -8652,8 +9395,10 @@
       <c r="D363" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="364" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E363" s="27"/>
+      <c r="F363" s="27"/>
+    </row>
+    <row r="364" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A364" s="16">
         <v>1144895271</v>
       </c>
@@ -8666,8 +9411,10 @@
       <c r="D364" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="365" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E364" s="27"/>
+      <c r="F364" s="27"/>
+    </row>
+    <row r="365" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A365" s="16">
         <v>1143159521</v>
       </c>
@@ -8680,8 +9427,10 @@
       <c r="D365" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="366" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E365" s="27"/>
+      <c r="F365" s="27"/>
+    </row>
+    <row r="366" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A366" s="16">
         <v>1146071111</v>
       </c>
@@ -8694,8 +9443,10 @@
       <c r="D366" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="367" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E366" s="27"/>
+      <c r="F366" s="27"/>
+    </row>
+    <row r="367" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A367" s="16">
         <v>1145848105</v>
       </c>
@@ -8708,8 +9459,10 @@
       <c r="D367" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="368" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E367" s="27"/>
+      <c r="F367" s="27"/>
+    </row>
+    <row r="368" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A368" s="16">
         <v>1143225678</v>
       </c>
@@ -8722,8 +9475,10 @@
       <c r="D368" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="369" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E368" s="27"/>
+      <c r="F368" s="27"/>
+    </row>
+    <row r="369" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A369" s="16">
         <v>1146339906</v>
       </c>
@@ -8736,8 +9491,10 @@
       <c r="D369" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="370" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E369" s="27"/>
+      <c r="F369" s="27"/>
+    </row>
+    <row r="370" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A370" s="16">
         <v>1141514644</v>
       </c>
@@ -8750,8 +9507,10 @@
       <c r="D370" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="371" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E370" s="27"/>
+      <c r="F370" s="27"/>
+    </row>
+    <row r="371" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A371" s="16">
         <v>1139056251</v>
       </c>
@@ -8764,8 +9523,10 @@
       <c r="D371" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="372" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E371" s="27"/>
+      <c r="F371" s="27"/>
+    </row>
+    <row r="372" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A372" s="16">
         <v>1144121710</v>
       </c>
@@ -8778,8 +9539,10 @@
       <c r="D372" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="373" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E372" s="27"/>
+      <c r="F372" s="27"/>
+    </row>
+    <row r="373" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A373" s="16">
         <v>1144625629</v>
       </c>
@@ -8792,8 +9555,10 @@
       <c r="D373" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="374" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E373" s="27"/>
+      <c r="F373" s="27"/>
+    </row>
+    <row r="374" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A374" s="16">
         <v>1143921680</v>
       </c>
@@ -8806,8 +9571,10 @@
       <c r="D374" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="375" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E374" s="27"/>
+      <c r="F374" s="27"/>
+    </row>
+    <row r="375" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A375" s="16">
         <v>1143867453</v>
       </c>
@@ -8820,8 +9587,10 @@
       <c r="D375" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="376" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E375" s="27"/>
+      <c r="F375" s="27"/>
+    </row>
+    <row r="376" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A376" s="16">
         <v>1154643173</v>
       </c>
@@ -8834,8 +9603,10 @@
       <c r="D376" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="377" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E376" s="27"/>
+      <c r="F376" s="27"/>
+    </row>
+    <row r="377" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A377" s="16">
         <v>1144748645</v>
       </c>
@@ -8848,8 +9619,10 @@
       <c r="D377" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="378" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E377" s="27"/>
+      <c r="F377" s="27"/>
+    </row>
+    <row r="378" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A378" s="16">
         <v>1142575768</v>
       </c>
@@ -8862,8 +9635,10 @@
       <c r="D378" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="379" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E378" s="27"/>
+      <c r="F378" s="27"/>
+    </row>
+    <row r="379" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A379" s="16">
         <v>1147418519</v>
       </c>
@@ -8876,8 +9651,10 @@
       <c r="D379" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="380" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E379" s="27"/>
+      <c r="F379" s="27"/>
+    </row>
+    <row r="380" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A380" s="16">
         <v>1142560703</v>
       </c>
@@ -8890,8 +9667,10 @@
       <c r="D380" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="381" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E380" s="27"/>
+      <c r="F380" s="27"/>
+    </row>
+    <row r="381" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A381" s="16">
         <v>1142621257</v>
       </c>
@@ -8904,8 +9683,10 @@
       <c r="D381" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="382" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E381" s="27"/>
+      <c r="F381" s="27"/>
+    </row>
+    <row r="382" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A382" s="16">
         <v>1144129531</v>
       </c>
@@ -8918,8 +9699,10 @@
       <c r="D382" s="19">
         <v>3</v>
       </c>
-    </row>
-    <row r="383" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E382" s="27"/>
+      <c r="F382" s="27"/>
+    </row>
+    <row r="383" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A383" s="16">
         <v>1149306035</v>
       </c>
@@ -8932,8 +9715,10 @@
       <c r="D383" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="384" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E383" s="27"/>
+      <c r="F383" s="27"/>
+    </row>
+    <row r="384" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A384" s="16">
         <v>1143337069</v>
       </c>
@@ -8946,8 +9731,10 @@
       <c r="D384" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="385" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E384" s="27"/>
+      <c r="F384" s="27"/>
+    </row>
+    <row r="385" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A385" s="16">
         <v>1145214647</v>
       </c>
@@ -8960,8 +9747,10 @@
       <c r="D385" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="386" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E385" s="27"/>
+      <c r="F385" s="27"/>
+    </row>
+    <row r="386" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A386" s="16">
         <v>1145994529</v>
       </c>
@@ -8974,8 +9763,10 @@
       <c r="D386" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="387" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E386" s="27"/>
+      <c r="F386" s="27"/>
+    </row>
+    <row r="387" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A387" s="16">
         <v>1146223472</v>
       </c>
@@ -8988,8 +9779,10 @@
       <c r="D387" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="388" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E387" s="27"/>
+      <c r="F387" s="27"/>
+    </row>
+    <row r="388" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A388" s="16">
         <v>1144765458</v>
       </c>
@@ -9002,8 +9795,10 @@
       <c r="D388" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="389" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E388" s="27"/>
+      <c r="F388" s="27"/>
+    </row>
+    <row r="389" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A389" s="16">
         <v>1144740527</v>
       </c>
@@ -9016,8 +9811,10 @@
       <c r="D389" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="390" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E389" s="27"/>
+      <c r="F389" s="27"/>
+    </row>
+    <row r="390" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A390" s="16">
         <v>1157570142</v>
       </c>
@@ -9030,8 +9827,10 @@
       <c r="D390" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="391" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E390" s="27"/>
+      <c r="F390" s="27"/>
+    </row>
+    <row r="391" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A391" s="16">
         <v>1145445324</v>
       </c>
@@ -9044,8 +9843,10 @@
       <c r="D391" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="392" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E391" s="27"/>
+      <c r="F391" s="27"/>
+    </row>
+    <row r="392" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A392" s="16">
         <v>1142934254</v>
       </c>
@@ -9058,8 +9859,10 @@
       <c r="D392" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="393" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E392" s="27"/>
+      <c r="F392" s="27"/>
+    </row>
+    <row r="393" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A393" s="16">
         <v>1142900800</v>
       </c>
@@ -9072,8 +9875,10 @@
       <c r="D393" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="394" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E393" s="27"/>
+      <c r="F393" s="27"/>
+    </row>
+    <row r="394" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A394" s="16">
         <v>1140211705</v>
       </c>
@@ -9086,8 +9891,10 @@
       <c r="D394" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="395" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E394" s="27"/>
+      <c r="F394" s="27"/>
+    </row>
+    <row r="395" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A395" s="16">
         <v>1144177480</v>
       </c>
@@ -9100,8 +9907,10 @@
       <c r="D395" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="396" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E395" s="27"/>
+      <c r="F395" s="27"/>
+    </row>
+    <row r="396" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A396" s="16">
         <v>1165185545</v>
       </c>
@@ -9114,8 +9923,10 @@
       <c r="D396" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="397" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E396" s="27"/>
+      <c r="F396" s="27"/>
+    </row>
+    <row r="397" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A397" s="16">
         <v>1144580154</v>
       </c>
@@ -9128,8 +9939,10 @@
       <c r="D397" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="398" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E397" s="27"/>
+      <c r="F397" s="27"/>
+    </row>
+    <row r="398" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A398" s="16">
         <v>1149677302</v>
       </c>
@@ -9142,8 +9955,10 @@
       <c r="D398" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="399" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E398" s="27"/>
+      <c r="F398" s="27"/>
+    </row>
+    <row r="399" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A399" s="16">
         <v>1150187175</v>
       </c>
@@ -9156,8 +9971,10 @@
       <c r="D399" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="400" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E399" s="27"/>
+      <c r="F399" s="27"/>
+    </row>
+    <row r="400" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A400" s="16">
         <v>1145199152</v>
       </c>
@@ -9170,8 +9987,10 @@
       <c r="D400" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="401" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E400" s="27"/>
+      <c r="F400" s="27"/>
+    </row>
+    <row r="401" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A401" s="16">
         <v>1141408425</v>
       </c>
@@ -9184,8 +10003,10 @@
       <c r="D401" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="402" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E401" s="27"/>
+      <c r="F401" s="27"/>
+    </row>
+    <row r="402" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A402" s="16">
         <v>1146629660</v>
       </c>
@@ -9198,8 +10019,10 @@
       <c r="D402" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="403" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E402" s="27"/>
+      <c r="F402" s="27"/>
+    </row>
+    <row r="403" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A403" s="16">
         <v>1144994587</v>
       </c>
@@ -9212,8 +10035,10 @@
       <c r="D403" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="404" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E403" s="27"/>
+      <c r="F403" s="27"/>
+    </row>
+    <row r="404" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A404" s="16">
         <v>1141834364</v>
       </c>
@@ -9226,8 +10051,10 @@
       <c r="D404" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="405" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E404" s="27"/>
+      <c r="F404" s="27"/>
+    </row>
+    <row r="405" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A405" s="16">
         <v>1149118836</v>
       </c>
@@ -9240,8 +10067,10 @@
       <c r="D405" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="406" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E405" s="27"/>
+      <c r="F405" s="27"/>
+    </row>
+    <row r="406" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A406" s="16">
         <v>1143808820</v>
       </c>
@@ -9254,8 +10083,10 @@
       <c r="D406" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="407" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E406" s="27"/>
+      <c r="F406" s="27"/>
+    </row>
+    <row r="407" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A407" s="16">
         <v>1138556111</v>
       </c>
@@ -9268,8 +10099,10 @@
       <c r="D407" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="408" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E407" s="27"/>
+      <c r="F407" s="27"/>
+    </row>
+    <row r="408" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A408" s="16">
         <v>1142388170</v>
       </c>
@@ -9282,8 +10115,10 @@
       <c r="D408" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="409" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E408" s="27"/>
+      <c r="F408" s="27"/>
+    </row>
+    <row r="409" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A409" s="16">
         <v>1144678529</v>
       </c>
@@ -9296,8 +10131,10 @@
       <c r="D409" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="410" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E409" s="27"/>
+      <c r="F409" s="27"/>
+    </row>
+    <row r="410" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A410" s="16">
         <v>1143899134</v>
       </c>
@@ -9310,8 +10147,10 @@
       <c r="D410" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="411" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E410" s="27"/>
+      <c r="F410" s="27"/>
+    </row>
+    <row r="411" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A411" s="16">
         <v>1143084893</v>
       </c>
@@ -9324,8 +10163,10 @@
       <c r="D411" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="412" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E411" s="27"/>
+      <c r="F411" s="27"/>
+    </row>
+    <row r="412" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A412" s="16">
         <v>2368991572</v>
       </c>
@@ -9338,8 +10179,10 @@
       <c r="D412" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="413" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E412" s="27"/>
+      <c r="F412" s="27"/>
+    </row>
+    <row r="413" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A413" s="16">
         <v>1148971516</v>
       </c>
@@ -9352,8 +10195,10 @@
       <c r="D413" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="414" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E413" s="27"/>
+      <c r="F413" s="27"/>
+    </row>
+    <row r="414" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A414" s="16">
         <v>1142710373</v>
       </c>
@@ -9366,8 +10211,10 @@
       <c r="D414" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="415" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E414" s="27"/>
+      <c r="F414" s="27"/>
+    </row>
+    <row r="415" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A415" s="16">
         <v>1144798079</v>
       </c>
@@ -9380,8 +10227,10 @@
       <c r="D415" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="416" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E415" s="27"/>
+      <c r="F415" s="27"/>
+    </row>
+    <row r="416" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A416" s="16">
         <v>1144129655</v>
       </c>
@@ -9394,8 +10243,10 @@
       <c r="D416" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="417" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E416" s="27"/>
+      <c r="F416" s="27"/>
+    </row>
+    <row r="417" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A417" s="16">
         <v>1144847314</v>
       </c>
@@ -9408,8 +10259,10 @@
       <c r="D417" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="418" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E417" s="27"/>
+      <c r="F417" s="27"/>
+    </row>
+    <row r="418" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A418" s="16">
         <v>1142964368</v>
       </c>
@@ -9422,8 +10275,10 @@
       <c r="D418" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="419" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E418" s="27"/>
+      <c r="F418" s="27"/>
+    </row>
+    <row r="419" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A419" s="16">
         <v>1144256391</v>
       </c>
@@ -9436,8 +10291,10 @@
       <c r="D419" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="420" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E419" s="27"/>
+      <c r="F419" s="27"/>
+    </row>
+    <row r="420" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A420" s="16">
         <v>1148572371</v>
       </c>
@@ -9450,8 +10307,10 @@
       <c r="D420" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="421" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E420" s="27"/>
+      <c r="F420" s="27"/>
+    </row>
+    <row r="421" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A421" s="16">
         <v>1150788238</v>
       </c>
@@ -9464,8 +10323,10 @@
       <c r="D421" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="422" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E421" s="27"/>
+      <c r="F421" s="27"/>
+    </row>
+    <row r="422" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A422" s="16">
         <v>1146104334</v>
       </c>
@@ -9478,8 +10339,10 @@
       <c r="D422" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="423" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E422" s="27"/>
+      <c r="F422" s="27"/>
+    </row>
+    <row r="423" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A423" s="16">
         <v>1143424057</v>
       </c>
@@ -9492,8 +10355,10 @@
       <c r="D423" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="424" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E423" s="27"/>
+      <c r="F423" s="27"/>
+    </row>
+    <row r="424" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A424" s="16">
         <v>1145771158</v>
       </c>
@@ -9506,8 +10371,10 @@
       <c r="D424" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="425" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E424" s="27"/>
+      <c r="F424" s="27"/>
+    </row>
+    <row r="425" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A425" s="16">
         <v>1143392882</v>
       </c>
@@ -9520,8 +10387,10 @@
       <c r="D425" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="426" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E425" s="27"/>
+      <c r="F425" s="27"/>
+    </row>
+    <row r="426" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A426" s="16">
         <v>2344110396</v>
       </c>
@@ -9534,8 +10403,10 @@
       <c r="D426" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="427" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E426" s="27"/>
+      <c r="F426" s="27"/>
+    </row>
+    <row r="427" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A427" s="16">
         <v>1142432630</v>
       </c>
@@ -9548,8 +10419,10 @@
       <c r="D427" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="428" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E427" s="27"/>
+      <c r="F427" s="27"/>
+    </row>
+    <row r="428" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A428" s="16">
         <v>1142508280</v>
       </c>
@@ -9562,8 +10435,10 @@
       <c r="D428" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="429" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E428" s="27"/>
+      <c r="F428" s="27"/>
+    </row>
+    <row r="429" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A429" s="16">
         <v>1143141115</v>
       </c>
@@ -9576,8 +10451,10 @@
       <c r="D429" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="430" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E429" s="27"/>
+      <c r="F429" s="27"/>
+    </row>
+    <row r="430" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A430" s="16">
         <v>1144280599</v>
       </c>
@@ -9590,8 +10467,10 @@
       <c r="D430" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="431" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E430" s="27"/>
+      <c r="F430" s="27"/>
+    </row>
+    <row r="431" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A431" s="16">
         <v>2368543720</v>
       </c>
@@ -9604,8 +10483,10 @@
       <c r="D431" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="432" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E431" s="27"/>
+      <c r="F431" s="27"/>
+    </row>
+    <row r="432" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A432" s="16">
         <v>1142736592</v>
       </c>
@@ -9618,8 +10499,10 @@
       <c r="D432" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="433" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E432" s="27"/>
+      <c r="F432" s="27"/>
+    </row>
+    <row r="433" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A433" s="16">
         <v>1143534442</v>
       </c>
@@ -9632,8 +10515,10 @@
       <c r="D433" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="434" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E433" s="27"/>
+      <c r="F433" s="27"/>
+    </row>
+    <row r="434" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A434" s="16">
         <v>1170135303</v>
       </c>
@@ -9646,8 +10531,10 @@
       <c r="D434" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="435" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E434" s="27"/>
+      <c r="F434" s="27"/>
+    </row>
+    <row r="435" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A435" s="16">
         <v>1163128331</v>
       </c>
@@ -9660,8 +10547,10 @@
       <c r="D435" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="436" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E435" s="27"/>
+      <c r="F435" s="27"/>
+    </row>
+    <row r="436" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A436" s="16">
         <v>1146611429</v>
       </c>
@@ -9674,8 +10563,10 @@
       <c r="D436" s="19">
         <v>5</v>
       </c>
-    </row>
-    <row r="437" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E436" s="27"/>
+      <c r="F436" s="27"/>
+    </row>
+    <row r="437" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A437" s="16">
         <v>1146005184</v>
       </c>
@@ -9688,8 +10579,10 @@
       <c r="D437" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="438" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E437" s="27"/>
+      <c r="F437" s="27"/>
+    </row>
+    <row r="438" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A438" s="16">
         <v>1144216676</v>
       </c>
@@ -9702,8 +10595,10 @@
       <c r="D438" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="439" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E438" s="27"/>
+      <c r="F438" s="27"/>
+    </row>
+    <row r="439" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A439" s="16">
         <v>1145659049</v>
       </c>
@@ -9716,8 +10611,10 @@
       <c r="D439" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="440" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E439" s="27"/>
+      <c r="F439" s="27"/>
+    </row>
+    <row r="440" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A440" s="16">
         <v>1141246213</v>
       </c>
@@ -9730,8 +10627,10 @@
       <c r="D440" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="441" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E440" s="27"/>
+      <c r="F440" s="27"/>
+    </row>
+    <row r="441" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A441" s="16">
         <v>1148803933</v>
       </c>
@@ -9744,8 +10643,10 @@
       <c r="D441" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="442" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E441" s="27"/>
+      <c r="F441" s="27"/>
+    </row>
+    <row r="442" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A442" s="16">
         <v>1142801099</v>
       </c>
@@ -9758,8 +10659,10 @@
       <c r="D442" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="443" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E442" s="27"/>
+      <c r="F442" s="27"/>
+    </row>
+    <row r="443" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A443" s="16">
         <v>1165337542</v>
       </c>
@@ -9772,8 +10675,10 @@
       <c r="D443" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="444" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E443" s="27"/>
+      <c r="F443" s="27"/>
+    </row>
+    <row r="444" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A444" s="16">
         <v>1143405932</v>
       </c>
@@ -9786,8 +10691,10 @@
       <c r="D444" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="445" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E444" s="27"/>
+      <c r="F444" s="27"/>
+    </row>
+    <row r="445" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A445" s="16">
         <v>1143240677</v>
       </c>
@@ -9800,8 +10707,10 @@
       <c r="D445" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="446" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E445" s="27"/>
+      <c r="F445" s="27"/>
+    </row>
+    <row r="446" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A446" s="16">
         <v>1144292586</v>
       </c>
@@ -9814,8 +10723,10 @@
       <c r="D446" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="447" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E446" s="27"/>
+      <c r="F446" s="27"/>
+    </row>
+    <row r="447" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A447" s="16">
         <v>1142745601</v>
       </c>
@@ -9828,8 +10739,10 @@
       <c r="D447" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="448" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E447" s="27"/>
+      <c r="F447" s="27"/>
+    </row>
+    <row r="448" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A448" s="16">
         <v>1144559083</v>
       </c>
@@ -9842,8 +10755,10 @@
       <c r="D448" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="449" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E448" s="27"/>
+      <c r="F448" s="27"/>
+    </row>
+    <row r="449" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A449" s="16">
         <v>1144847108</v>
       </c>
@@ -9856,8 +10771,10 @@
       <c r="D449" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="450" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E449" s="27"/>
+      <c r="F449" s="27"/>
+    </row>
+    <row r="450" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A450" s="16">
         <v>1153709348</v>
       </c>
@@ -9870,8 +10787,10 @@
       <c r="D450" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="451" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E450" s="27"/>
+      <c r="F450" s="27"/>
+    </row>
+    <row r="451" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A451" s="16">
         <v>1145363980</v>
       </c>
@@ -9884,8 +10803,10 @@
       <c r="D451" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="452" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E451" s="27"/>
+      <c r="F451" s="27"/>
+    </row>
+    <row r="452" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A452" s="16">
         <v>1147428609</v>
       </c>
@@ -9898,8 +10819,10 @@
       <c r="D452" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="453" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E452" s="27"/>
+      <c r="F452" s="27"/>
+    </row>
+    <row r="453" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A453" s="16">
         <v>1145924120</v>
       </c>
@@ -9912,8 +10835,10 @@
       <c r="D453" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="454" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E453" s="27"/>
+      <c r="F453" s="27"/>
+    </row>
+    <row r="454" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A454" s="16">
         <v>1144996368</v>
       </c>
@@ -9926,8 +10851,10 @@
       <c r="D454" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="455" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E454" s="27"/>
+      <c r="F454" s="27"/>
+    </row>
+    <row r="455" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A455" s="16">
         <v>1143866810</v>
       </c>
@@ -9940,8 +10867,10 @@
       <c r="D455" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="456" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E455" s="27"/>
+      <c r="F455" s="27"/>
+    </row>
+    <row r="456" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A456" s="16">
         <v>1145471635</v>
       </c>
@@ -9954,8 +10883,10 @@
       <c r="D456" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="457" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E456" s="27"/>
+      <c r="F456" s="27"/>
+    </row>
+    <row r="457" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A457" s="16">
         <v>1142644614</v>
       </c>
@@ -9968,8 +10899,10 @@
       <c r="D457" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="458" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E457" s="27"/>
+      <c r="F457" s="27"/>
+    </row>
+    <row r="458" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A458" s="16">
         <v>1144768056</v>
       </c>
@@ -9982,8 +10915,10 @@
       <c r="D458" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="459" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E458" s="27"/>
+      <c r="F458" s="27"/>
+    </row>
+    <row r="459" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A459" s="16">
         <v>1144239678</v>
       </c>
@@ -9996,8 +10931,10 @@
       <c r="D459" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="460" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E459" s="27"/>
+      <c r="F459" s="27"/>
+    </row>
+    <row r="460" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A460" s="16">
         <v>2583150400</v>
       </c>
@@ -10010,8 +10947,10 @@
       <c r="D460" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="461" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E460" s="27"/>
+      <c r="F460" s="27"/>
+    </row>
+    <row r="461" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A461" s="16">
         <v>1143470076</v>
       </c>
@@ -10024,8 +10963,10 @@
       <c r="D461" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="462" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E461" s="27"/>
+      <c r="F461" s="27"/>
+    </row>
+    <row r="462" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A462" s="16">
         <v>1143877528</v>
       </c>
@@ -10038,8 +10979,10 @@
       <c r="D462" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="463" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E462" s="27"/>
+      <c r="F462" s="27"/>
+    </row>
+    <row r="463" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A463" s="16">
         <v>1143422648</v>
       </c>
@@ -10052,8 +10995,10 @@
       <c r="D463" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="464" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E463" s="27"/>
+      <c r="F463" s="27"/>
+    </row>
+    <row r="464" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A464" s="16">
         <v>1144739644</v>
       </c>
@@ -10066,8 +11011,10 @@
       <c r="D464" s="19">
         <v>6</v>
       </c>
-    </row>
-    <row r="465" spans="1:4" ht="19" customHeight="1" thickBot="1">
+      <c r="E464" s="27"/>
+      <c r="F464" s="27"/>
+    </row>
+    <row r="465" spans="1:6" ht="19" customHeight="1" thickBot="1">
       <c r="A465" s="16">
         <v>1143331195</v>
       </c>
@@ -10080,13 +11027,15 @@
       <c r="D465" s="19">
         <v>6</v>
       </c>
+      <c r="E465" s="27"/>
+      <c r="F465" s="27"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{D6DB9536-A956-4EEE-91B9-0D4523217CC8}"/>
-    <hyperlink ref="F2" r:id="rId2" xr:uid="{1C42E57A-4625-47F5-ABB6-8F43E64F8276}"/>
-    <hyperlink ref="E3:E10" r:id="rId3" display="taaanet@gmail.com" xr:uid="{30E40290-5536-4913-8335-C5133F55DD5B}"/>
-    <hyperlink ref="F3:F10" r:id="rId4" display="taanet@hotmail.com" xr:uid="{9C4162B4-D513-44F2-BBF7-08BBFC7D336E}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{D6DB9536-A956-4EEE-91B9-0D4523217CC8}"/>
+    <hyperlink ref="H2" r:id="rId2" xr:uid="{1C42E57A-4625-47F5-ABB6-8F43E64F8276}"/>
+    <hyperlink ref="G3:G10" r:id="rId3" display="taaanet@gmail.com" xr:uid="{30E40290-5536-4913-8335-C5133F55DD5B}"/>
+    <hyperlink ref="H3:H10" r:id="rId4" display="taanet@hotmail.com" xr:uid="{9C4162B4-D513-44F2-BBF7-08BBFC7D336E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId5"/>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T.MOHAMMED13\Desktop\sss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2B1C30-1B2E-400A-9B06-A35F19F6E4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B052DA-E5D4-4F41-BE1A-04BA5B4BAFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="477">
   <si>
     <t>الأول الثانوي</t>
   </si>
@@ -1727,10 +1727,10 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3203,8 +3203,12 @@
       </c>
       <c r="E11" s="27"/>
       <c r="F11" s="27"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="G11" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A12" s="16">
@@ -3221,8 +3225,12 @@
       </c>
       <c r="E12" s="27"/>
       <c r="F12" s="27"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="G12" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A13" s="16">
@@ -3239,8 +3247,12 @@
       </c>
       <c r="E13" s="27"/>
       <c r="F13" s="27"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="G13" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A14" s="16">
@@ -3257,8 +3269,12 @@
       </c>
       <c r="E14" s="27"/>
       <c r="F14" s="27"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="G14" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H14" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A15" s="16">
@@ -3275,8 +3291,12 @@
       </c>
       <c r="E15" s="27"/>
       <c r="F15" s="27"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
+      <c r="G15" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A16" s="16">
@@ -3293,8 +3313,12 @@
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="G16" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A17" s="16">
@@ -3311,8 +3335,12 @@
       </c>
       <c r="E17" s="27"/>
       <c r="F17" s="27"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="G17" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H17" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A18" s="16">
@@ -3329,8 +3357,12 @@
       </c>
       <c r="E18" s="27"/>
       <c r="F18" s="27"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
+      <c r="G18" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H18" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A19" s="16">
@@ -3347,8 +3379,12 @@
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+      <c r="G19" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H19" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A20" s="16">
@@ -3365,8 +3401,12 @@
       </c>
       <c r="E20" s="27"/>
       <c r="F20" s="27"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+      <c r="G20" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H20" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A21" s="16">
@@ -3383,8 +3423,12 @@
       </c>
       <c r="E21" s="27"/>
       <c r="F21" s="27"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+      <c r="G21" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H21" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A22" s="16">
@@ -3401,8 +3445,12 @@
       </c>
       <c r="E22" s="27"/>
       <c r="F22" s="27"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
+      <c r="G22" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A23" s="16">
@@ -3419,8 +3467,12 @@
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="27"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
+      <c r="G23" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H23" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="24" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A24" s="16">
@@ -3437,8 +3489,12 @@
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
+      <c r="G24" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H24" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A25" s="16">
@@ -3455,8 +3511,12 @@
       </c>
       <c r="E25" s="27"/>
       <c r="F25" s="27"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+      <c r="G25" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H25" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A26" s="17">
@@ -3473,8 +3533,12 @@
       </c>
       <c r="E26" s="27"/>
       <c r="F26" s="27"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
+      <c r="G26" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H26" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A27" s="16">
@@ -3491,8 +3555,12 @@
       </c>
       <c r="E27" s="27"/>
       <c r="F27" s="27"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+      <c r="G27" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H27" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A28" s="16">
@@ -3509,8 +3577,12 @@
       </c>
       <c r="E28" s="27"/>
       <c r="F28" s="27"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="G28" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H28" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A29" s="16">
@@ -3527,8 +3599,12 @@
       </c>
       <c r="E29" s="27"/>
       <c r="F29" s="27"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
+      <c r="G29" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H29" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="30" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A30" s="16">
@@ -3545,8 +3621,12 @@
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="27"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
+      <c r="G30" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H30" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A31" s="16">
@@ -3563,8 +3643,12 @@
       </c>
       <c r="E31" s="27"/>
       <c r="F31" s="27"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
+      <c r="G31" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H31" s="25" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="32" spans="1:8" ht="19" customHeight="1" thickBot="1">
       <c r="A32" s="16">
@@ -11034,8 +11118,8 @@
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{D6DB9536-A956-4EEE-91B9-0D4523217CC8}"/>
     <hyperlink ref="H2" r:id="rId2" xr:uid="{1C42E57A-4625-47F5-ABB6-8F43E64F8276}"/>
-    <hyperlink ref="G3:G10" r:id="rId3" display="taaanet@gmail.com" xr:uid="{30E40290-5536-4913-8335-C5133F55DD5B}"/>
-    <hyperlink ref="H3:H10" r:id="rId4" display="taanet@hotmail.com" xr:uid="{9C4162B4-D513-44F2-BBF7-08BBFC7D336E}"/>
+    <hyperlink ref="G3:G31" r:id="rId3" display="taaanet@gmail.com" xr:uid="{64B1A971-ABEC-495A-9FC3-D7346F67D8F0}"/>
+    <hyperlink ref="H3:H31" r:id="rId4" display="taanet@hotmail.com" xr:uid="{D6EDC24B-27E0-437D-B15D-4CF260A6C66E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId5"/>
